--- a/research/traditional_assets/database/data/mexico/mexico_transportation.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_transportation.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1021423579961048</v>
+        <v>0.1018674309221164</v>
       </c>
       <c r="C2">
-        <v>4187.580502960394</v>
+        <v>4151.018617521113</v>
       </c>
       <c r="D2">
-        <v>2694.280502960394</v>
+        <v>2700.027617521113</v>
       </c>
       <c r="E2">
-        <v>-653</v>
+        <v>-610.691</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>42.309</v>
       </c>
       <c r="G2">
         <v>1493.3</v>
@@ -1457,28 +1457,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1281427</v>
       </c>
       <c r="N2">
-        <v>664.2768888888888</v>
+        <v>662.1487461888888</v>
       </c>
       <c r="O2">
-        <v>199.2830666666667</v>
+        <v>198.6446238566666</v>
       </c>
       <c r="P2">
-        <v>464.9938222222222</v>
+        <v>463.5041223322222</v>
       </c>
       <c r="Q2">
-        <v>465.6058222222222</v>
+        <v>464.1161223322222</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1021423579961048</v>
+        <v>0.1025407383051681</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8256468788271011</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>312.1392606280062</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1018674309221164</v>
+        <v>0.1015925038481282</v>
       </c>
       <c r="C3">
-        <v>4151.018617521113</v>
+        <v>4114.481302597425</v>
       </c>
       <c r="D3">
-        <v>2700.027617521113</v>
+        <v>2705.799302597426</v>
       </c>
       <c r="E3">
-        <v>-610.691</v>
+        <v>-568.3820000000001</v>
       </c>
       <c r="F3">
-        <v>42.309</v>
+        <v>84.61799999999999</v>
       </c>
       <c r="G3">
         <v>1493.3</v>
@@ -1539,28 +1539,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M3">
-        <v>2.1281427</v>
+        <v>4.256285399999999</v>
       </c>
       <c r="N3">
-        <v>662.1487461888888</v>
+        <v>660.0206034888888</v>
       </c>
       <c r="O3">
-        <v>198.6446238566666</v>
+        <v>198.0061810466666</v>
       </c>
       <c r="P3">
-        <v>463.5041223322222</v>
+        <v>462.0144224422222</v>
       </c>
       <c r="Q3">
-        <v>464.1161223322222</v>
+        <v>462.6264224422222</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1025407383051681</v>
+        <v>0.1029472488246206</v>
       </c>
       <c r="T3">
-        <v>0.8256468788271011</v>
+        <v>0.8315621022031371</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>312.1392606280062</v>
+        <v>156.0696303140031</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1015925038481282</v>
+        <v>0.1013175767741398</v>
       </c>
       <c r="C4">
-        <v>4114.481302597425</v>
+        <v>4077.96871609558</v>
       </c>
       <c r="D4">
-        <v>2705.799302597426</v>
+        <v>2711.59571609558</v>
       </c>
       <c r="E4">
-        <v>-568.3820000000001</v>
+        <v>-526.073</v>
       </c>
       <c r="F4">
-        <v>84.61799999999999</v>
+        <v>126.927</v>
       </c>
       <c r="G4">
         <v>1493.3</v>
@@ -1621,28 +1621,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M4">
-        <v>4.256285399999999</v>
+        <v>6.384428099999998</v>
       </c>
       <c r="N4">
-        <v>660.0206034888888</v>
+        <v>657.8924607888888</v>
       </c>
       <c r="O4">
-        <v>198.0061810466666</v>
+        <v>197.3677382366666</v>
       </c>
       <c r="P4">
-        <v>462.0144224422222</v>
+        <v>460.5247225522222</v>
       </c>
       <c r="Q4">
-        <v>462.6264224422222</v>
+        <v>461.1367225522222</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1029472488246206</v>
+        <v>0.1033621410042679</v>
       </c>
       <c r="T4">
-        <v>0.8315621022031371</v>
+        <v>0.837599288947751</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>156.0696303140031</v>
+        <v>104.0464202093354</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1013175767741398</v>
+        <v>0.1010426497001515</v>
       </c>
       <c r="C5">
-        <v>4077.96871609558</v>
+        <v>4041.481017277799</v>
       </c>
       <c r="D5">
-        <v>2711.59571609558</v>
+        <v>2717.417017277799</v>
       </c>
       <c r="E5">
-        <v>-526.073</v>
+        <v>-483.764</v>
       </c>
       <c r="F5">
-        <v>126.927</v>
+        <v>169.236</v>
       </c>
       <c r="G5">
         <v>1493.3</v>
@@ -1703,28 +1703,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M5">
-        <v>6.384428099999998</v>
+        <v>8.512570799999999</v>
       </c>
       <c r="N5">
-        <v>657.8924607888888</v>
+        <v>655.7643180888888</v>
       </c>
       <c r="O5">
-        <v>197.3677382366666</v>
+        <v>196.7292954266666</v>
       </c>
       <c r="P5">
-        <v>460.5247225522222</v>
+        <v>459.0350226622222</v>
       </c>
       <c r="Q5">
-        <v>461.1367225522222</v>
+        <v>459.6470226622222</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1033621410042679</v>
+        <v>0.1037856767709912</v>
       </c>
       <c r="T5">
-        <v>0.837599288947751</v>
+        <v>0.8437622504162112</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>104.0464202093354</v>
+        <v>78.03481515700156</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1010426497001515</v>
+        <v>0.1007677226261632</v>
       </c>
       <c r="C6">
-        <v>4041.481017277799</v>
+        <v>4005.018366776883</v>
       </c>
       <c r="D6">
-        <v>2717.417017277799</v>
+        <v>2723.263366776883</v>
       </c>
       <c r="E6">
-        <v>-483.764</v>
+        <v>-441.455</v>
       </c>
       <c r="F6">
-        <v>169.236</v>
+        <v>211.545</v>
       </c>
       <c r="G6">
         <v>1493.3</v>
@@ -1785,28 +1785,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M6">
-        <v>8.512570799999999</v>
+        <v>10.6407135</v>
       </c>
       <c r="N6">
-        <v>655.7643180888888</v>
+        <v>653.6361753888889</v>
       </c>
       <c r="O6">
-        <v>196.7292954266666</v>
+        <v>196.0908526166667</v>
       </c>
       <c r="P6">
-        <v>459.0350226622222</v>
+        <v>457.5453227722222</v>
       </c>
       <c r="Q6">
-        <v>459.6470226622222</v>
+        <v>458.1573227722222</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1037856767709912</v>
+        <v>0.1042181290801718</v>
       </c>
       <c r="T6">
-        <v>0.8437622504162112</v>
+        <v>0.8500549584419022</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>78.03481515700156</v>
+        <v>62.42785212560126</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1007677226261632</v>
+        <v>0.1004927955521749</v>
       </c>
       <c r="C7">
-        <v>4005.018366776883</v>
+        <v>3968.580926610974</v>
       </c>
       <c r="D7">
-        <v>2723.263366776883</v>
+        <v>2729.134926610974</v>
       </c>
       <c r="E7">
-        <v>-441.455</v>
+        <v>-399.146</v>
       </c>
       <c r="F7">
-        <v>211.545</v>
+        <v>253.854</v>
       </c>
       <c r="G7">
         <v>1493.3</v>
@@ -1867,28 +1867,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M7">
-        <v>10.6407135</v>
+        <v>12.7688562</v>
       </c>
       <c r="N7">
-        <v>653.6361753888889</v>
+        <v>651.5080326888889</v>
       </c>
       <c r="O7">
-        <v>196.0908526166667</v>
+        <v>195.4524098066667</v>
       </c>
       <c r="P7">
-        <v>457.5453227722222</v>
+        <v>456.0556228822222</v>
       </c>
       <c r="Q7">
-        <v>458.1573227722222</v>
+        <v>456.6676228822222</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1042181290801718</v>
+        <v>0.1046597825023137</v>
       </c>
       <c r="T7">
-        <v>0.8500549584419022</v>
+        <v>0.856481553872395</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.42785212560126</v>
+        <v>52.02321010466771</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1004927955521749</v>
+        <v>0.1002178684781866</v>
       </c>
       <c r="C8">
-        <v>3968.580926610974</v>
+        <v>3932.168860198527</v>
       </c>
       <c r="D8">
-        <v>2729.134926610974</v>
+        <v>2735.031860198528</v>
       </c>
       <c r="E8">
-        <v>-399.1460000000001</v>
+        <v>-356.837</v>
       </c>
       <c r="F8">
-        <v>253.854</v>
+        <v>296.163</v>
       </c>
       <c r="G8">
         <v>1493.3</v>
@@ -1949,28 +1949,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M8">
-        <v>12.7688562</v>
+        <v>14.8969989</v>
       </c>
       <c r="N8">
-        <v>651.5080326888889</v>
+        <v>649.3798899888889</v>
       </c>
       <c r="O8">
-        <v>195.4524098066667</v>
+        <v>194.8139669966667</v>
       </c>
       <c r="P8">
-        <v>456.0556228822222</v>
+        <v>454.5659229922222</v>
       </c>
       <c r="Q8">
-        <v>456.6676228822222</v>
+        <v>455.1779229922222</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1046597825023137</v>
+        <v>0.1051109338475124</v>
       </c>
       <c r="T8">
-        <v>0.856481553872395</v>
+        <v>0.8630463556562319</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.02321010466772</v>
+        <v>44.59132294685804</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1002178684781866</v>
+        <v>0.09994294140419827</v>
       </c>
       <c r="C9">
-        <v>3932.168860198528</v>
+        <v>3895.782332373473</v>
       </c>
       <c r="D9">
-        <v>2735.031860198528</v>
+        <v>2740.954332373473</v>
       </c>
       <c r="E9">
-        <v>-356.837</v>
+        <v>-314.528</v>
       </c>
       <c r="F9">
-        <v>296.163</v>
+        <v>338.472</v>
       </c>
       <c r="G9">
         <v>1493.3</v>
@@ -2031,28 +2031,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M9">
-        <v>14.8969989</v>
+        <v>17.0251416</v>
       </c>
       <c r="N9">
-        <v>649.3798899888889</v>
+        <v>647.2517472888889</v>
       </c>
       <c r="O9">
-        <v>194.8139669966667</v>
+        <v>194.1755241866666</v>
       </c>
       <c r="P9">
-        <v>454.5659229922222</v>
+        <v>453.0762231022222</v>
       </c>
       <c r="Q9">
-        <v>455.1779229922222</v>
+        <v>453.6882231022223</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1051109338475124</v>
+        <v>0.1055718928306503</v>
       </c>
       <c r="T9">
-        <v>0.8630463556562319</v>
+        <v>0.869753870522326</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.59132294685804</v>
+        <v>39.01740757850078</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09994294140419827</v>
+        <v>0.09966801433020996</v>
       </c>
       <c r="C10">
-        <v>3895.782332373473</v>
+        <v>3859.421509400569</v>
       </c>
       <c r="D10">
-        <v>2740.954332373473</v>
+        <v>2746.90250940057</v>
       </c>
       <c r="E10">
-        <v>-314.528</v>
+        <v>-272.2190000000001</v>
       </c>
       <c r="F10">
-        <v>338.472</v>
+        <v>380.7809999999999</v>
       </c>
       <c r="G10">
         <v>1493.3</v>
@@ -2113,28 +2113,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M10">
-        <v>17.0251416</v>
+        <v>19.1532843</v>
       </c>
       <c r="N10">
-        <v>647.2517472888889</v>
+        <v>645.1236045888888</v>
       </c>
       <c r="O10">
-        <v>194.1755241866666</v>
+        <v>193.5370813766666</v>
       </c>
       <c r="P10">
-        <v>453.0762231022222</v>
+        <v>451.5865232122222</v>
       </c>
       <c r="Q10">
-        <v>453.6882231022223</v>
+        <v>452.1985232122223</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1055718928306503</v>
+        <v>0.1060429827804505</v>
       </c>
       <c r="T10">
-        <v>0.869753870522326</v>
+        <v>0.8766088032975649</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.01740757850078</v>
+        <v>34.68214006977848</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09966801433020996</v>
+        <v>0.09939308725622163</v>
       </c>
       <c r="C11">
-        <v>3859.421509400569</v>
+        <v>3823.086558990972</v>
       </c>
       <c r="D11">
-        <v>2746.90250940057</v>
+        <v>2752.876558990972</v>
       </c>
       <c r="E11">
-        <v>-272.2190000000001</v>
+        <v>-229.9100000000001</v>
       </c>
       <c r="F11">
-        <v>380.7809999999999</v>
+        <v>423.0899999999999</v>
       </c>
       <c r="G11">
         <v>1493.3</v>
@@ -2195,28 +2195,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M11">
-        <v>19.1532843</v>
+        <v>21.28142699999999</v>
       </c>
       <c r="N11">
-        <v>645.1236045888888</v>
+        <v>642.9954618888888</v>
       </c>
       <c r="O11">
-        <v>193.5370813766666</v>
+        <v>192.8986385666666</v>
       </c>
       <c r="P11">
-        <v>451.5865232122222</v>
+        <v>450.0968233222222</v>
       </c>
       <c r="Q11">
-        <v>452.1985232122223</v>
+        <v>450.7088233222222</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1060429827804505</v>
+        <v>0.1065245413958018</v>
       </c>
       <c r="T11">
-        <v>0.8766088032975649</v>
+        <v>0.8836160679122537</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.68214006977848</v>
+        <v>31.21392606280063</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09939308725622163</v>
+        <v>0.09911816018223331</v>
       </c>
       <c r="C12">
-        <v>3823.086558990972</v>
+        <v>3786.777650317983</v>
       </c>
       <c r="D12">
-        <v>2752.876558990972</v>
+        <v>2758.876650317983</v>
       </c>
       <c r="E12">
-        <v>-229.91</v>
+        <v>-187.6010000000001</v>
       </c>
       <c r="F12">
-        <v>423.09</v>
+        <v>465.3989999999999</v>
       </c>
       <c r="G12">
         <v>1493.3</v>
@@ -2277,28 +2277,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M12">
-        <v>21.281427</v>
+        <v>23.4095697</v>
       </c>
       <c r="N12">
-        <v>642.9954618888888</v>
+        <v>640.8673191888888</v>
       </c>
       <c r="O12">
-        <v>192.8986385666666</v>
+        <v>192.2601957566666</v>
       </c>
       <c r="P12">
-        <v>450.0968233222222</v>
+        <v>448.6071234322222</v>
       </c>
       <c r="Q12">
-        <v>450.7088233222222</v>
+        <v>449.2191234322222</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1065245413958018</v>
+        <v>0.1070169215530711</v>
       </c>
       <c r="T12">
-        <v>0.8836160679122537</v>
+        <v>0.8907807991474972</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.21392606280062</v>
+        <v>28.37629642072784</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09911816018223331</v>
+        <v>0.098843233108245</v>
       </c>
       <c r="C13">
-        <v>3786.777650317983</v>
+        <v>3750.494954033033</v>
       </c>
       <c r="D13">
-        <v>2758.876650317983</v>
+        <v>2764.902954033033</v>
       </c>
       <c r="E13">
-        <v>-187.6010000000001</v>
+        <v>-145.2920000000001</v>
       </c>
       <c r="F13">
-        <v>465.3989999999999</v>
+        <v>507.7079999999999</v>
       </c>
       <c r="G13">
         <v>1493.3</v>
@@ -2359,28 +2359,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M13">
-        <v>23.4095697</v>
+        <v>25.53771239999999</v>
       </c>
       <c r="N13">
-        <v>640.8673191888888</v>
+        <v>638.7391764888888</v>
       </c>
       <c r="O13">
-        <v>192.2601957566666</v>
+        <v>191.6217529466666</v>
       </c>
       <c r="P13">
-        <v>448.6071234322222</v>
+        <v>447.1174235422221</v>
       </c>
       <c r="Q13">
-        <v>449.2191234322222</v>
+        <v>447.7294235422222</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1070169215530711</v>
+        <v>0.1075204921684602</v>
       </c>
       <c r="T13">
-        <v>0.8907807991474972</v>
+        <v>0.8981083651835419</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.37629642072784</v>
+        <v>26.01160505233386</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.098843233108245</v>
+        <v>0.09856830603425669</v>
       </c>
       <c r="C14">
-        <v>3750.494954033033</v>
+        <v>3714.238642281853</v>
       </c>
       <c r="D14">
-        <v>2764.902954033033</v>
+        <v>2770.955642281853</v>
       </c>
       <c r="E14">
-        <v>-145.2920000000001</v>
+        <v>-102.9830000000001</v>
       </c>
       <c r="F14">
-        <v>507.7079999999999</v>
+        <v>550.0169999999999</v>
       </c>
       <c r="G14">
         <v>1493.3</v>
@@ -2441,28 +2441,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M14">
-        <v>25.53771239999999</v>
+        <v>27.66585509999999</v>
       </c>
       <c r="N14">
-        <v>638.7391764888888</v>
+        <v>636.6110337888888</v>
       </c>
       <c r="O14">
-        <v>191.6217529466666</v>
+        <v>190.9833101366666</v>
       </c>
       <c r="P14">
-        <v>447.1174235422221</v>
+        <v>445.6277236522221</v>
       </c>
       <c r="Q14">
-        <v>447.7294235422222</v>
+        <v>446.2397236522222</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1075204921684602</v>
+        <v>0.1080356391198353</v>
       </c>
       <c r="T14">
-        <v>0.8981083651835419</v>
+        <v>0.9056043810135184</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.01160505233386</v>
+        <v>24.01071235600048</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09856830603425669</v>
+        <v>0.09829337896026837</v>
       </c>
       <c r="C15">
-        <v>3714.238642281853</v>
+        <v>3678.008888720866</v>
       </c>
       <c r="D15">
-        <v>2770.955642281853</v>
+        <v>2777.034888720866</v>
       </c>
       <c r="E15">
-        <v>-102.9830000000001</v>
+        <v>-60.67399999999998</v>
       </c>
       <c r="F15">
-        <v>550.0169999999999</v>
+        <v>592.326</v>
       </c>
       <c r="G15">
         <v>1493.3</v>
@@ -2523,28 +2523,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M15">
-        <v>27.66585509999999</v>
+        <v>29.7939978</v>
       </c>
       <c r="N15">
-        <v>636.6110337888888</v>
+        <v>634.4828910888889</v>
       </c>
       <c r="O15">
-        <v>190.9833101366666</v>
+        <v>190.3448673266667</v>
       </c>
       <c r="P15">
-        <v>445.6277236522221</v>
+        <v>444.1380237622222</v>
       </c>
       <c r="Q15">
-        <v>446.2397236522222</v>
+        <v>444.7500237622223</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1080356391198353</v>
+        <v>0.1085627662328702</v>
       </c>
       <c r="T15">
-        <v>0.9056043810135184</v>
+        <v>0.9132747227930293</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.01071235600048</v>
+        <v>22.29566147342902</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09829337896026837</v>
+        <v>0.09801845188628006</v>
       </c>
       <c r="C16">
-        <v>3678.008888720866</v>
+        <v>3641.805868533799</v>
       </c>
       <c r="D16">
-        <v>2777.034888720866</v>
+        <v>2783.140868533799</v>
       </c>
       <c r="E16">
-        <v>-60.67399999999998</v>
+        <v>-18.36500000000001</v>
       </c>
       <c r="F16">
-        <v>592.326</v>
+        <v>634.635</v>
       </c>
       <c r="G16">
         <v>1493.3</v>
@@ -2605,28 +2605,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M16">
-        <v>29.7939978</v>
+        <v>31.9221405</v>
       </c>
       <c r="N16">
-        <v>634.4828910888889</v>
+        <v>632.3547483888889</v>
       </c>
       <c r="O16">
-        <v>190.3448673266667</v>
+        <v>189.7064245166667</v>
       </c>
       <c r="P16">
-        <v>444.1380237622222</v>
+        <v>442.6483238722222</v>
       </c>
       <c r="Q16">
-        <v>444.7500237622223</v>
+        <v>443.2603238722223</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1085627662328702</v>
+        <v>0.1091022963368001</v>
       </c>
       <c r="T16">
-        <v>0.9132747227930293</v>
+        <v>0.9211255432026465</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.29566147342902</v>
+        <v>20.80928404186708</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09801845188628006</v>
+        <v>0.09774352481229175</v>
       </c>
       <c r="C17">
-        <v>3641.8058685338</v>
+        <v>3605.629758448508</v>
       </c>
       <c r="D17">
-        <v>2783.140868533799</v>
+        <v>2789.273758448508</v>
       </c>
       <c r="E17">
-        <v>-18.36500000000012</v>
+        <v>23.94399999999996</v>
       </c>
       <c r="F17">
-        <v>634.6349999999999</v>
+        <v>676.944</v>
       </c>
       <c r="G17">
         <v>1493.3</v>
@@ -2687,28 +2687,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M17">
-        <v>31.92214049999999</v>
+        <v>34.0502832</v>
       </c>
       <c r="N17">
-        <v>632.3547483888889</v>
+        <v>630.2266056888889</v>
       </c>
       <c r="O17">
-        <v>189.7064245166667</v>
+        <v>189.0679817066666</v>
       </c>
       <c r="P17">
-        <v>442.6483238722222</v>
+        <v>441.1586239822223</v>
       </c>
       <c r="Q17">
-        <v>443.2603238722223</v>
+        <v>441.7706239822223</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1091022963368001</v>
+        <v>0.1096546723955854</v>
       </c>
       <c r="T17">
-        <v>0.9211255432026465</v>
+        <v>0.9291632879077306</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.80928404186709</v>
+        <v>19.50870378925039</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09774352481229175</v>
+        <v>0.09746859773830342</v>
       </c>
       <c r="C18">
-        <v>3605.629758448508</v>
+        <v>3569.480736754029</v>
       </c>
       <c r="D18">
-        <v>2789.273758448508</v>
+        <v>2795.433736754029</v>
       </c>
       <c r="E18">
-        <v>23.94399999999996</v>
+        <v>66.25300000000004</v>
       </c>
       <c r="F18">
-        <v>676.944</v>
+        <v>719.253</v>
       </c>
       <c r="G18">
         <v>1493.3</v>
@@ -2769,28 +2769,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M18">
-        <v>34.0502832</v>
+        <v>36.1784259</v>
       </c>
       <c r="N18">
-        <v>630.2266056888889</v>
+        <v>628.0984629888889</v>
       </c>
       <c r="O18">
-        <v>189.0679817066666</v>
+        <v>188.4295388966667</v>
       </c>
       <c r="P18">
-        <v>441.1586239822223</v>
+        <v>439.6689240922222</v>
       </c>
       <c r="Q18">
-        <v>441.7706239822223</v>
+        <v>440.2809240922222</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1096546723955854</v>
+        <v>0.1102203587208475</v>
       </c>
       <c r="T18">
-        <v>0.9291632879077306</v>
+        <v>0.9373947132081182</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.50870378925039</v>
+        <v>18.36113297811801</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09746859773830342</v>
+        <v>0.09719367066431511</v>
       </c>
       <c r="C19">
-        <v>3569.480736754029</v>
+        <v>3533.358983317855</v>
       </c>
       <c r="D19">
-        <v>2795.433736754029</v>
+        <v>2801.620983317855</v>
       </c>
       <c r="E19">
-        <v>66.25300000000004</v>
+        <v>108.562</v>
       </c>
       <c r="F19">
-        <v>719.253</v>
+        <v>761.562</v>
       </c>
       <c r="G19">
         <v>1493.3</v>
@@ -2851,28 +2851,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M19">
-        <v>36.1784259</v>
+        <v>38.3065686</v>
       </c>
       <c r="N19">
-        <v>628.0984629888889</v>
+        <v>625.9703202888888</v>
       </c>
       <c r="O19">
-        <v>188.4295388966667</v>
+        <v>187.7910960866666</v>
       </c>
       <c r="P19">
-        <v>439.6689240922222</v>
+        <v>438.1792242022222</v>
       </c>
       <c r="Q19">
-        <v>440.2809240922222</v>
+        <v>438.7912242022222</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1102203587208475</v>
+        <v>0.110799842273555</v>
       </c>
       <c r="T19">
-        <v>0.9373947132081182</v>
+        <v>0.9458269049792466</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.36113297811801</v>
+        <v>17.34107003488923</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09719367066431513</v>
+        <v>0.0969187435903268</v>
       </c>
       <c r="C20">
-        <v>3533.358983317854</v>
+        <v>3497.264679603442</v>
       </c>
       <c r="D20">
-        <v>2801.620983317854</v>
+        <v>2807.835679603442</v>
       </c>
       <c r="E20">
-        <v>108.5619999999999</v>
+        <v>150.871</v>
       </c>
       <c r="F20">
-        <v>761.5619999999999</v>
+        <v>803.871</v>
       </c>
       <c r="G20">
         <v>1493.3</v>
@@ -2933,28 +2933,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M20">
-        <v>38.30656859999999</v>
+        <v>40.4347113</v>
       </c>
       <c r="N20">
-        <v>625.9703202888888</v>
+        <v>623.8421775888888</v>
       </c>
       <c r="O20">
-        <v>187.7910960866666</v>
+        <v>187.1526532766667</v>
       </c>
       <c r="P20">
-        <v>438.1792242022222</v>
+        <v>436.6895243122221</v>
       </c>
       <c r="Q20">
-        <v>438.7912242022222</v>
+        <v>437.3015243122222</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.110799842273555</v>
+        <v>0.1113936340621318</v>
       </c>
       <c r="T20">
-        <v>0.9458269049792466</v>
+        <v>0.9544672990163289</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.34107003488924</v>
+        <v>16.42838213831612</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0969187435903268</v>
+        <v>0.09664381651633849</v>
       </c>
       <c r="C21">
-        <v>3497.264679603442</v>
+        <v>3461.198008687956</v>
       </c>
       <c r="D21">
-        <v>2807.835679603442</v>
+        <v>2814.078008687956</v>
       </c>
       <c r="E21">
-        <v>150.871</v>
+        <v>193.1799999999999</v>
       </c>
       <c r="F21">
-        <v>803.871</v>
+        <v>846.1799999999999</v>
       </c>
       <c r="G21">
         <v>1493.3</v>
@@ -3015,28 +3015,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M21">
-        <v>40.4347113</v>
+        <v>42.56285399999999</v>
       </c>
       <c r="N21">
-        <v>623.8421775888888</v>
+        <v>621.7140348888888</v>
       </c>
       <c r="O21">
-        <v>187.1526532766667</v>
+        <v>186.5142104666666</v>
       </c>
       <c r="P21">
-        <v>436.6895243122221</v>
+        <v>435.1998244222222</v>
       </c>
       <c r="Q21">
-        <v>437.3015243122222</v>
+        <v>435.8118244222222</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1113936340621318</v>
+        <v>0.1120022706454231</v>
       </c>
       <c r="T21">
-        <v>0.9544672990163289</v>
+        <v>0.9633237029043384</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.42838213831612</v>
+        <v>15.60696303140031</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09664381651633849</v>
+        <v>0.09636888944235018</v>
       </c>
       <c r="C22">
-        <v>3461.198008687956</v>
+        <v>3425.159155280241</v>
       </c>
       <c r="D22">
-        <v>2814.078008687956</v>
+        <v>2820.34815528024</v>
       </c>
       <c r="E22">
-        <v>193.1799999999999</v>
+        <v>235.489</v>
       </c>
       <c r="F22">
-        <v>846.1799999999999</v>
+        <v>888.489</v>
       </c>
       <c r="G22">
         <v>1493.3</v>
@@ -3097,28 +3097,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M22">
-        <v>42.56285399999999</v>
+        <v>44.6909967</v>
       </c>
       <c r="N22">
-        <v>621.7140348888888</v>
+        <v>619.5858921888888</v>
       </c>
       <c r="O22">
-        <v>186.5142104666666</v>
+        <v>185.8757676566666</v>
       </c>
       <c r="P22">
-        <v>435.1998244222222</v>
+        <v>433.7101245322222</v>
       </c>
       <c r="Q22">
-        <v>435.8118244222222</v>
+        <v>434.3221245322222</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1120022706454231</v>
+        <v>0.1126263157498104</v>
       </c>
       <c r="T22">
-        <v>0.9633237029043384</v>
+        <v>0.9724043195490064</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.60696303140031</v>
+        <v>14.86377431561934</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09636888944235017</v>
+        <v>0.09609396236836185</v>
       </c>
       <c r="C23">
-        <v>3425.159155280241</v>
+        <v>3389.148305739042</v>
       </c>
       <c r="D23">
-        <v>2820.34815528024</v>
+        <v>2826.646305739042</v>
       </c>
       <c r="E23">
-        <v>235.4889999999999</v>
+        <v>277.7979999999999</v>
       </c>
       <c r="F23">
-        <v>888.4889999999999</v>
+        <v>930.7979999999999</v>
       </c>
       <c r="G23">
         <v>1493.3</v>
@@ -3179,28 +3179,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M23">
-        <v>44.69099669999999</v>
+        <v>46.81913939999999</v>
       </c>
       <c r="N23">
-        <v>619.5858921888888</v>
+        <v>617.4577494888888</v>
       </c>
       <c r="O23">
-        <v>185.8757676566666</v>
+        <v>185.2373248466666</v>
       </c>
       <c r="P23">
-        <v>433.7101245322222</v>
+        <v>432.2204246422222</v>
       </c>
       <c r="Q23">
-        <v>434.3221245322222</v>
+        <v>432.8324246422222</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1126263157498103</v>
+        <v>0.1132663620107203</v>
       </c>
       <c r="T23">
-        <v>0.9724043195490062</v>
+        <v>0.9817177725178964</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.86377431561935</v>
+        <v>14.18814821036392</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09609396236836185</v>
+        <v>0.09581903529437355</v>
       </c>
       <c r="C24">
-        <v>3389.148305739042</v>
+        <v>3353.165648091473</v>
       </c>
       <c r="D24">
-        <v>2826.646305739042</v>
+        <v>2832.972648091473</v>
       </c>
       <c r="E24">
-        <v>277.7979999999999</v>
+        <v>320.107</v>
       </c>
       <c r="F24">
-        <v>930.7979999999999</v>
+        <v>973.107</v>
       </c>
       <c r="G24">
         <v>1493.3</v>
@@ -3261,28 +3261,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M24">
-        <v>46.81913939999999</v>
+        <v>48.9472821</v>
       </c>
       <c r="N24">
-        <v>617.4577494888888</v>
+        <v>615.3296067888889</v>
       </c>
       <c r="O24">
-        <v>185.2373248466666</v>
+        <v>184.5988820366667</v>
       </c>
       <c r="P24">
-        <v>432.2204246422222</v>
+        <v>430.7307247522223</v>
       </c>
       <c r="Q24">
-        <v>432.8324246422222</v>
+        <v>431.3427247522223</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1132663620107203</v>
+        <v>0.1139230328498358</v>
       </c>
       <c r="T24">
-        <v>0.9817177725178964</v>
+        <v>0.9912731333561083</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.18814821036392</v>
+        <v>13.57127220121766</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09581903529437355</v>
+        <v>0.09554410822038523</v>
       </c>
       <c r="C25">
-        <v>3353.165648091473</v>
+        <v>3317.211372051722</v>
       </c>
       <c r="D25">
-        <v>2832.972648091473</v>
+        <v>2839.327372051722</v>
       </c>
       <c r="E25">
-        <v>320.107</v>
+        <v>362.4159999999999</v>
       </c>
       <c r="F25">
-        <v>973.107</v>
+        <v>1015.416</v>
       </c>
       <c r="G25">
         <v>1493.3</v>
@@ -3343,28 +3343,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M25">
-        <v>48.9472821</v>
+        <v>51.07542479999999</v>
       </c>
       <c r="N25">
-        <v>615.3296067888889</v>
+        <v>613.2014640888889</v>
       </c>
       <c r="O25">
-        <v>184.5988820366667</v>
+        <v>183.9604392266667</v>
       </c>
       <c r="P25">
-        <v>430.7307247522223</v>
+        <v>429.2410248622222</v>
       </c>
       <c r="Q25">
-        <v>431.3427247522223</v>
+        <v>429.8530248622222</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1139230328498358</v>
+        <v>0.1145969845005069</v>
       </c>
       <c r="T25">
-        <v>0.9912731333561083</v>
+        <v>1.001079951058484</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.57127220121766</v>
+        <v>13.00580252616693</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09554410822038523</v>
+        <v>0.09553168114639692</v>
       </c>
       <c r="C26">
-        <v>3317.211372051722</v>
+        <v>3275.190287646227</v>
       </c>
       <c r="D26">
-        <v>2839.327372051722</v>
+        <v>2839.615287646227</v>
       </c>
       <c r="E26">
-        <v>362.4159999999998</v>
+        <v>404.7249999999999</v>
       </c>
       <c r="F26">
-        <v>1015.416</v>
+        <v>1057.725</v>
       </c>
       <c r="G26">
         <v>1493.3</v>
@@ -3425,45 +3425,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M26">
-        <v>51.07542479999999</v>
+        <v>54.79015499999999</v>
       </c>
       <c r="N26">
-        <v>613.2014640888889</v>
+        <v>609.4867338888888</v>
       </c>
       <c r="O26">
-        <v>183.9604392266667</v>
+        <v>182.8460201666666</v>
       </c>
       <c r="P26">
-        <v>429.2410248622222</v>
+        <v>426.6407137222221</v>
       </c>
       <c r="Q26">
-        <v>429.8530248622222</v>
+        <v>427.2527137222222</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1145969845005069</v>
+        <v>0.1152889081951959</v>
       </c>
       <c r="T26">
-        <v>1.001079951058484</v>
+        <v>1.011148283899589</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.00580252616693</v>
+        <v>12.12401915798356</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09553168114639692</v>
+        <v>0.09526725407240859</v>
       </c>
       <c r="C27">
-        <v>3275.190287646227</v>
+        <v>3239.021513422383</v>
       </c>
       <c r="D27">
-        <v>2839.615287646227</v>
+        <v>2845.755513422383</v>
       </c>
       <c r="E27">
-        <v>404.7249999999999</v>
+        <v>447.0339999999999</v>
       </c>
       <c r="F27">
-        <v>1057.725</v>
+        <v>1100.034</v>
       </c>
       <c r="G27">
         <v>1493.3</v>
@@ -3507,28 +3507,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M27">
-        <v>54.79015499999999</v>
+        <v>56.98176119999999</v>
       </c>
       <c r="N27">
-        <v>609.4867338888888</v>
+        <v>607.2951276888889</v>
       </c>
       <c r="O27">
-        <v>182.8460201666666</v>
+        <v>182.1885383066667</v>
       </c>
       <c r="P27">
-        <v>426.6407137222221</v>
+        <v>425.1065893822222</v>
       </c>
       <c r="Q27">
-        <v>427.2527137222222</v>
+        <v>425.7185893822223</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1152889081951959</v>
+        <v>0.1159995325302819</v>
       </c>
       <c r="T27">
-        <v>1.011148283899589</v>
+        <v>1.021488733844508</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.12401915798356</v>
+        <v>11.65771072883035</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09526725407240859</v>
+        <v>0.09500282699842028</v>
       </c>
       <c r="C28">
-        <v>3239.021513422383</v>
+        <v>3202.879351306821</v>
       </c>
       <c r="D28">
-        <v>2845.755513422383</v>
+        <v>2851.922351306821</v>
       </c>
       <c r="E28">
-        <v>447.0339999999999</v>
+        <v>489.3430000000001</v>
       </c>
       <c r="F28">
-        <v>1100.034</v>
+        <v>1142.343</v>
       </c>
       <c r="G28">
         <v>1493.3</v>
@@ -3589,28 +3589,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M28">
-        <v>56.98176119999999</v>
+        <v>59.1733674</v>
       </c>
       <c r="N28">
-        <v>607.2951276888889</v>
+        <v>605.1035214888889</v>
       </c>
       <c r="O28">
-        <v>182.1885383066667</v>
+        <v>181.5310564466667</v>
       </c>
       <c r="P28">
-        <v>425.1065893822222</v>
+        <v>423.5724650422222</v>
       </c>
       <c r="Q28">
-        <v>425.7185893822223</v>
+        <v>424.1844650422223</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1159995325302819</v>
+        <v>0.1167296260252333</v>
       </c>
       <c r="T28">
-        <v>1.021488733844508</v>
+        <v>1.032112483787919</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.65771072883035</v>
+        <v>11.22594366479959</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09500282699842028</v>
+        <v>0.09473839992443196</v>
       </c>
       <c r="C29">
-        <v>3202.879351306821</v>
+        <v>3166.76397468299</v>
       </c>
       <c r="D29">
-        <v>2851.922351306821</v>
+        <v>2858.11597468299</v>
       </c>
       <c r="E29">
-        <v>489.3430000000001</v>
+        <v>531.652</v>
       </c>
       <c r="F29">
-        <v>1142.343</v>
+        <v>1184.652</v>
       </c>
       <c r="G29">
         <v>1493.3</v>
@@ -3671,28 +3671,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M29">
-        <v>59.1733674</v>
+        <v>61.3649736</v>
       </c>
       <c r="N29">
-        <v>605.1035214888889</v>
+        <v>602.9119152888888</v>
       </c>
       <c r="O29">
-        <v>181.5310564466667</v>
+        <v>180.8735745866666</v>
       </c>
       <c r="P29">
-        <v>423.5724650422222</v>
+        <v>422.0383407022222</v>
       </c>
       <c r="Q29">
-        <v>424.1844650422223</v>
+        <v>422.6503407022222</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1167296260252333</v>
+        <v>0.1174799998950444</v>
       </c>
       <c r="T29">
-        <v>1.032112483787919</v>
+        <v>1.043031337896423</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.22594366479959</v>
+        <v>10.82501710534247</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09473839992443196</v>
+        <v>0.09447397285044364</v>
       </c>
       <c r="C30">
-        <v>3166.76397468299</v>
+        <v>3130.675558443788</v>
       </c>
       <c r="D30">
-        <v>2858.11597468299</v>
+        <v>2864.336558443788</v>
       </c>
       <c r="E30">
-        <v>531.652</v>
+        <v>573.961</v>
       </c>
       <c r="F30">
-        <v>1184.652</v>
+        <v>1226.961</v>
       </c>
       <c r="G30">
         <v>1493.3</v>
@@ -3753,28 +3753,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M30">
-        <v>61.3649736</v>
+        <v>63.5565798</v>
       </c>
       <c r="N30">
-        <v>602.9119152888888</v>
+        <v>600.7203090888888</v>
       </c>
       <c r="O30">
-        <v>180.8735745866666</v>
+        <v>180.2160927266666</v>
       </c>
       <c r="P30">
-        <v>422.0383407022222</v>
+        <v>420.5042163622222</v>
       </c>
       <c r="Q30">
-        <v>422.6503407022222</v>
+        <v>421.1162163622222</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1174799998950444</v>
+        <v>0.1182515110569629</v>
       </c>
       <c r="T30">
-        <v>1.043031337896423</v>
+        <v>1.054257765360097</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.82501710534247</v>
+        <v>10.4517406534341</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09447397285044364</v>
+        <v>0.09420954577645534</v>
       </c>
       <c r="C31">
-        <v>3130.675558443788</v>
+        <v>3094.614279008023</v>
       </c>
       <c r="D31">
-        <v>2864.336558443788</v>
+        <v>2870.584279008022</v>
       </c>
       <c r="E31">
-        <v>573.9609999999998</v>
+        <v>616.2699999999998</v>
       </c>
       <c r="F31">
-        <v>1226.961</v>
+        <v>1269.27</v>
       </c>
       <c r="G31">
         <v>1493.3</v>
@@ -3835,28 +3835,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M31">
-        <v>63.55657979999999</v>
+        <v>65.74818599999999</v>
       </c>
       <c r="N31">
-        <v>600.7203090888888</v>
+        <v>598.5287028888888</v>
       </c>
       <c r="O31">
-        <v>180.2160927266666</v>
+        <v>179.5586108666666</v>
       </c>
       <c r="P31">
-        <v>420.5042163622222</v>
+        <v>418.9700920222222</v>
       </c>
       <c r="Q31">
-        <v>421.1162163622222</v>
+        <v>419.5820920222222</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1182515110569629</v>
+        <v>0.1190450653949362</v>
       </c>
       <c r="T31">
-        <v>1.054257765360097</v>
+        <v>1.065804947894162</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.45174065343411</v>
+        <v>10.10334929831964</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09420954577645534</v>
+        <v>0.094314018702467</v>
       </c>
       <c r="C32">
-        <v>3094.614279008023</v>
+        <v>3049.833602739576</v>
       </c>
       <c r="D32">
-        <v>2870.584279008022</v>
+        <v>2868.112602739576</v>
       </c>
       <c r="E32">
-        <v>616.2699999999998</v>
+        <v>658.579</v>
       </c>
       <c r="F32">
-        <v>1269.27</v>
+        <v>1311.579</v>
       </c>
       <c r="G32">
         <v>1493.3</v>
@@ -3917,45 +3917,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M32">
-        <v>65.74818599999999</v>
+        <v>70.1694765</v>
       </c>
       <c r="N32">
-        <v>598.5287028888888</v>
+        <v>594.1074123888889</v>
       </c>
       <c r="O32">
-        <v>179.5586108666666</v>
+        <v>178.2322237166667</v>
       </c>
       <c r="P32">
-        <v>418.9700920222222</v>
+        <v>415.8751886722222</v>
       </c>
       <c r="Q32">
-        <v>419.5820920222222</v>
+        <v>416.4871886722222</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1190450653949362</v>
+        <v>0.1198616213079232</v>
       </c>
       <c r="T32">
-        <v>1.065804947894162</v>
+        <v>1.077686831371242</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.10334929831964</v>
+        <v>9.466749960559971</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.094314018702467</v>
+        <v>0.0940614916284787</v>
       </c>
       <c r="C33">
-        <v>3049.833602739576</v>
+        <v>3013.50632840744</v>
       </c>
       <c r="D33">
-        <v>2868.112602739576</v>
+        <v>2874.09432840744</v>
       </c>
       <c r="E33">
-        <v>658.579</v>
+        <v>700.8879999999999</v>
       </c>
       <c r="F33">
-        <v>1311.579</v>
+        <v>1353.888</v>
       </c>
       <c r="G33">
         <v>1493.3</v>
@@ -3999,28 +3999,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M33">
-        <v>70.1694765</v>
+        <v>72.433008</v>
       </c>
       <c r="N33">
-        <v>594.1074123888889</v>
+        <v>591.8438808888889</v>
       </c>
       <c r="O33">
-        <v>178.2322237166667</v>
+        <v>177.5531642666666</v>
       </c>
       <c r="P33">
-        <v>415.8751886722222</v>
+        <v>414.2907166222222</v>
       </c>
       <c r="Q33">
-        <v>416.4871886722222</v>
+        <v>414.9027166222223</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1198616213079232</v>
+        <v>0.1207021935712922</v>
       </c>
       <c r="T33">
-        <v>1.077686831371242</v>
+        <v>1.089918182009414</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.466749960559971</v>
+        <v>9.170914024292472</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0940614916284787</v>
+        <v>0.09380896455449039</v>
       </c>
       <c r="C34">
-        <v>3013.50632840744</v>
+        <v>2977.20405715413</v>
       </c>
       <c r="D34">
-        <v>2874.09432840744</v>
+        <v>2880.101057154131</v>
       </c>
       <c r="E34">
-        <v>700.8879999999999</v>
+        <v>743.1969999999999</v>
       </c>
       <c r="F34">
-        <v>1353.888</v>
+        <v>1396.197</v>
       </c>
       <c r="G34">
         <v>1493.3</v>
@@ -4081,28 +4081,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M34">
-        <v>72.433008</v>
+        <v>74.69653949999999</v>
       </c>
       <c r="N34">
-        <v>591.8438808888889</v>
+        <v>589.5803493888889</v>
       </c>
       <c r="O34">
-        <v>177.5531642666666</v>
+        <v>176.8741048166667</v>
       </c>
       <c r="P34">
-        <v>414.2907166222222</v>
+        <v>412.7062445722222</v>
       </c>
       <c r="Q34">
-        <v>414.9027166222223</v>
+        <v>413.3182445722222</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1207021935712922</v>
+        <v>0.1215678575440155</v>
       </c>
       <c r="T34">
-        <v>1.089918182009414</v>
+        <v>1.102514647592009</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.170914024292472</v>
+        <v>8.893007538707852</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09380896455449039</v>
+        <v>0.09355643748050206</v>
       </c>
       <c r="C35">
-        <v>2977.20405715413</v>
+        <v>2940.926946073921</v>
       </c>
       <c r="D35">
-        <v>2880.101057154131</v>
+        <v>2886.132946073921</v>
       </c>
       <c r="E35">
-        <v>743.1969999999999</v>
+        <v>785.5060000000001</v>
       </c>
       <c r="F35">
-        <v>1396.197</v>
+        <v>1438.506</v>
       </c>
       <c r="G35">
         <v>1493.3</v>
@@ -4163,28 +4163,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M35">
-        <v>74.69653949999999</v>
+        <v>76.960071</v>
       </c>
       <c r="N35">
-        <v>589.5803493888889</v>
+        <v>587.3168178888889</v>
       </c>
       <c r="O35">
-        <v>176.8741048166667</v>
+        <v>176.1950453666666</v>
       </c>
       <c r="P35">
-        <v>412.7062445722222</v>
+        <v>411.1217725222222</v>
       </c>
       <c r="Q35">
-        <v>413.3182445722222</v>
+        <v>411.7337725222222</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1215678575440155</v>
+        <v>0.1224597537583365</v>
       </c>
       <c r="T35">
-        <v>1.102514647592009</v>
+        <v>1.115492824252864</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.893007538707852</v>
+        <v>8.631448493451739</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09355643748050206</v>
+        <v>0.09330391040651376</v>
       </c>
       <c r="C36">
-        <v>2940.926946073921</v>
+        <v>2904.675153579876</v>
       </c>
       <c r="D36">
-        <v>2886.132946073921</v>
+        <v>2892.190153579877</v>
       </c>
       <c r="E36">
-        <v>785.5060000000001</v>
+        <v>827.8150000000001</v>
       </c>
       <c r="F36">
-        <v>1438.506</v>
+        <v>1480.815</v>
       </c>
       <c r="G36">
         <v>1493.3</v>
@@ -4245,28 +4245,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M36">
-        <v>76.960071</v>
+        <v>79.2236025</v>
       </c>
       <c r="N36">
-        <v>587.3168178888889</v>
+        <v>585.0532863888889</v>
       </c>
       <c r="O36">
-        <v>176.1950453666666</v>
+        <v>175.5159859166667</v>
       </c>
       <c r="P36">
-        <v>411.1217725222222</v>
+        <v>409.5373004722222</v>
       </c>
       <c r="Q36">
-        <v>411.7337725222222</v>
+        <v>410.1493004722223</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1224597537583365</v>
+        <v>0.1233790929330981</v>
       </c>
       <c r="T36">
-        <v>1.115492824252864</v>
+        <v>1.128870329426361</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.631448493451739</v>
+        <v>8.384835679353117</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09330391040651376</v>
+        <v>0.09305138333252547</v>
       </c>
       <c r="C37">
-        <v>2904.675153579876</v>
+        <v>2868.448839417723</v>
       </c>
       <c r="D37">
-        <v>2892.190153579877</v>
+        <v>2898.272839417723</v>
       </c>
       <c r="E37">
-        <v>827.8150000000001</v>
+        <v>870.124</v>
       </c>
       <c r="F37">
-        <v>1480.815</v>
+        <v>1523.124</v>
       </c>
       <c r="G37">
         <v>1493.3</v>
@@ -4327,28 +4327,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M37">
-        <v>79.2236025</v>
+        <v>81.487134</v>
       </c>
       <c r="N37">
-        <v>585.0532863888889</v>
+        <v>582.7897548888889</v>
       </c>
       <c r="O37">
-        <v>175.5159859166667</v>
+        <v>174.8369264666667</v>
       </c>
       <c r="P37">
-        <v>409.5373004722222</v>
+        <v>407.9528284222222</v>
       </c>
       <c r="Q37">
-        <v>410.1493004722223</v>
+        <v>408.5648284222222</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1233790929330981</v>
+        <v>0.124327161457071</v>
       </c>
       <c r="T37">
-        <v>1.128870329426361</v>
+        <v>1.142665881636529</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.384835679353117</v>
+        <v>8.151923577148864</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09305138333252547</v>
+        <v>0.09279885625853714</v>
       </c>
       <c r="C38">
-        <v>2868.448839417723</v>
+        <v>2832.248164679893</v>
       </c>
       <c r="D38">
-        <v>2898.272839417723</v>
+        <v>2904.381164679893</v>
       </c>
       <c r="E38">
-        <v>870.1239999999998</v>
+        <v>912.4329999999998</v>
       </c>
       <c r="F38">
-        <v>1523.124</v>
+        <v>1565.433</v>
       </c>
       <c r="G38">
         <v>1493.3</v>
@@ -4409,28 +4409,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M38">
-        <v>81.48713399999998</v>
+        <v>83.75066549999998</v>
       </c>
       <c r="N38">
-        <v>582.7897548888889</v>
+        <v>580.5262233888889</v>
       </c>
       <c r="O38">
-        <v>174.8369264666667</v>
+        <v>174.1578670166666</v>
       </c>
       <c r="P38">
-        <v>407.9528284222222</v>
+        <v>406.3683563722223</v>
       </c>
       <c r="Q38">
-        <v>408.5648284222222</v>
+        <v>406.9803563722223</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.124327161457071</v>
+        <v>0.1253053273945034</v>
       </c>
       <c r="T38">
-        <v>1.142665881636529</v>
+        <v>1.156899387885115</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.151923577148866</v>
+        <v>7.931601318307004</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09279885625853714</v>
+        <v>0.09254632918454883</v>
       </c>
       <c r="C39">
-        <v>2832.248164679893</v>
+        <v>2796.073291819739</v>
       </c>
       <c r="D39">
-        <v>2904.381164679893</v>
+        <v>2910.515291819739</v>
       </c>
       <c r="E39">
-        <v>912.4329999999998</v>
+        <v>954.742</v>
       </c>
       <c r="F39">
-        <v>1565.433</v>
+        <v>1607.742</v>
       </c>
       <c r="G39">
         <v>1493.3</v>
@@ -4491,28 +4491,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M39">
-        <v>83.75066549999998</v>
+        <v>86.014197</v>
       </c>
       <c r="N39">
-        <v>580.5262233888889</v>
+        <v>578.2626918888889</v>
       </c>
       <c r="O39">
-        <v>174.1578670166666</v>
+        <v>173.4788075666667</v>
       </c>
       <c r="P39">
-        <v>406.3683563722223</v>
+        <v>404.7838843222222</v>
       </c>
       <c r="Q39">
-        <v>406.9803563722223</v>
+        <v>405.3958843222222</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1253053273945034</v>
+        <v>0.126315047071853</v>
       </c>
       <c r="T39">
-        <v>1.156899387885115</v>
+        <v>1.17159203949656</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.931601318307004</v>
+        <v>7.72287496782524</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09254632918454883</v>
+        <v>0.09251220211056052</v>
       </c>
       <c r="C40">
-        <v>2796.073291819739</v>
+        <v>2754.595259495125</v>
       </c>
       <c r="D40">
-        <v>2910.515291819739</v>
+        <v>2911.346259495124</v>
       </c>
       <c r="E40">
-        <v>954.742</v>
+        <v>997.0509999999999</v>
       </c>
       <c r="F40">
-        <v>1607.742</v>
+        <v>1650.051</v>
       </c>
       <c r="G40">
         <v>1493.3</v>
@@ -4573,45 +4573,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M40">
-        <v>86.014197</v>
+        <v>89.5977693</v>
       </c>
       <c r="N40">
-        <v>578.2626918888889</v>
+        <v>574.6791195888889</v>
       </c>
       <c r="O40">
-        <v>173.4788075666667</v>
+        <v>172.4037358766666</v>
       </c>
       <c r="P40">
-        <v>404.7838843222222</v>
+        <v>402.2753837122222</v>
       </c>
       <c r="Q40">
-        <v>405.3958843222222</v>
+        <v>402.8873837122222</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.126315047071853</v>
+        <v>0.1273578723123943</v>
       </c>
       <c r="T40">
-        <v>1.17159203949656</v>
+        <v>1.186766417390346</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.72287496782524</v>
+        <v>7.4139891436883</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09251220211056052</v>
+        <v>0.09226527503657218</v>
       </c>
       <c r="C41">
-        <v>2754.595259495125</v>
+        <v>2718.312907774352</v>
       </c>
       <c r="D41">
-        <v>2911.346259495124</v>
+        <v>2917.372907774352</v>
       </c>
       <c r="E41">
-        <v>997.0509999999999</v>
+        <v>1039.36</v>
       </c>
       <c r="F41">
-        <v>1650.051</v>
+        <v>1692.36</v>
       </c>
       <c r="G41">
         <v>1493.3</v>
@@ -4655,28 +4655,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M41">
-        <v>89.5977693</v>
+        <v>91.89514799999999</v>
       </c>
       <c r="N41">
-        <v>574.6791195888889</v>
+        <v>572.3817408888889</v>
       </c>
       <c r="O41">
-        <v>172.4037358766666</v>
+        <v>171.7145222666666</v>
       </c>
       <c r="P41">
-        <v>402.2753837122222</v>
+        <v>400.6672186222222</v>
       </c>
       <c r="Q41">
-        <v>402.8873837122222</v>
+        <v>401.2792186222222</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1273578723123943</v>
+        <v>0.128435458394287</v>
       </c>
       <c r="T41">
-        <v>1.186766417390346</v>
+        <v>1.202446607880593</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.4139891436883</v>
+        <v>7.228639415096094</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09226527503657218</v>
+        <v>0.09201834796258387</v>
       </c>
       <c r="C42">
-        <v>2718.312907774352</v>
+        <v>2682.055558803254</v>
       </c>
       <c r="D42">
-        <v>2917.372907774352</v>
+        <v>2923.424558803254</v>
       </c>
       <c r="E42">
-        <v>1039.36</v>
+        <v>1081.669</v>
       </c>
       <c r="F42">
-        <v>1692.36</v>
+        <v>1734.669</v>
       </c>
       <c r="G42">
         <v>1493.3</v>
@@ -4737,28 +4737,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M42">
-        <v>91.89514799999999</v>
+        <v>94.19252669999999</v>
       </c>
       <c r="N42">
-        <v>572.3817408888889</v>
+        <v>570.0843621888888</v>
       </c>
       <c r="O42">
-        <v>171.7145222666666</v>
+        <v>171.0253086566666</v>
       </c>
       <c r="P42">
-        <v>400.6672186222222</v>
+        <v>399.0590535322222</v>
       </c>
       <c r="Q42">
-        <v>401.2792186222222</v>
+        <v>399.6710535322222</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.128435458394287</v>
+        <v>0.1295495728179388</v>
       </c>
       <c r="T42">
-        <v>1.202446607880593</v>
+        <v>1.218658330251864</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.228639415096094</v>
+        <v>7.052331136679115</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09201834796258387</v>
+        <v>0.09177142088859556</v>
       </c>
       <c r="C43">
-        <v>2682.055558803254</v>
+        <v>2645.823368498579</v>
       </c>
       <c r="D43">
-        <v>2923.424558803254</v>
+        <v>2929.501368498579</v>
       </c>
       <c r="E43">
-        <v>1081.669</v>
+        <v>1123.978</v>
       </c>
       <c r="F43">
-        <v>1734.669</v>
+        <v>1776.978</v>
       </c>
       <c r="G43">
         <v>1493.3</v>
@@ -4819,28 +4819,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M43">
-        <v>94.19252669999999</v>
+        <v>96.48990540000001</v>
       </c>
       <c r="N43">
-        <v>570.0843621888888</v>
+        <v>567.7869834888888</v>
       </c>
       <c r="O43">
-        <v>171.0253086566666</v>
+        <v>170.3360950466667</v>
       </c>
       <c r="P43">
-        <v>399.0590535322222</v>
+        <v>397.4508884422222</v>
       </c>
       <c r="Q43">
-        <v>399.6710535322222</v>
+        <v>398.0628884422222</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1295495728179388</v>
+        <v>0.1307021049803372</v>
       </c>
       <c r="T43">
-        <v>1.218658330251864</v>
+        <v>1.23542907753249</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.052331136679115</v>
+        <v>6.884418490567707</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09177142088859558</v>
+        <v>0.09152449381460726</v>
       </c>
       <c r="C44">
-        <v>2645.823368498579</v>
+        <v>2609.616494076171</v>
       </c>
       <c r="D44">
-        <v>2929.501368498579</v>
+        <v>2935.603494076171</v>
       </c>
       <c r="E44">
-        <v>1123.978</v>
+        <v>1166.287</v>
       </c>
       <c r="F44">
-        <v>1776.978</v>
+        <v>1819.287</v>
       </c>
       <c r="G44">
         <v>1493.3</v>
@@ -4901,28 +4901,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M44">
-        <v>96.4899054</v>
+        <v>98.78728409999999</v>
       </c>
       <c r="N44">
-        <v>567.7869834888888</v>
+        <v>565.4896047888889</v>
       </c>
       <c r="O44">
-        <v>170.3360950466667</v>
+        <v>169.6468814366667</v>
       </c>
       <c r="P44">
-        <v>397.4508884422222</v>
+        <v>395.8427233522222</v>
       </c>
       <c r="Q44">
-        <v>398.0628884422222</v>
+        <v>396.4547233522222</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1307021049803372</v>
+        <v>0.131895076867732</v>
       </c>
       <c r="T44">
-        <v>1.23542907753249</v>
+        <v>1.25278827208612</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.884418490567707</v>
+        <v>6.72431573497311</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09152449381460726</v>
+        <v>0.09127756674061895</v>
       </c>
       <c r="C45">
-        <v>2609.616494076171</v>
+        <v>2573.435094064523</v>
       </c>
       <c r="D45">
-        <v>2935.603494076171</v>
+        <v>2941.731094064522</v>
       </c>
       <c r="E45">
-        <v>1166.287</v>
+        <v>1208.596</v>
       </c>
       <c r="F45">
-        <v>1819.287</v>
+        <v>1861.596</v>
       </c>
       <c r="G45">
         <v>1493.3</v>
@@ -4983,28 +4983,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M45">
-        <v>98.78728409999999</v>
+        <v>101.0846628</v>
       </c>
       <c r="N45">
-        <v>565.4896047888889</v>
+        <v>563.1922260888889</v>
       </c>
       <c r="O45">
-        <v>169.6468814366667</v>
+        <v>168.9576678266667</v>
       </c>
       <c r="P45">
-        <v>395.8427233522222</v>
+        <v>394.2345582622222</v>
       </c>
       <c r="Q45">
-        <v>396.4547233522222</v>
+        <v>394.8465582622222</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.131895076867732</v>
+        <v>0.1331306548939624</v>
       </c>
       <c r="T45">
-        <v>1.25278827208612</v>
+        <v>1.270767437873808</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.72431573497311</v>
+        <v>6.571490377360085</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09127756674061895</v>
+        <v>0.09103063966663064</v>
       </c>
       <c r="C46">
-        <v>2573.435094064523</v>
+        <v>2537.279328318508</v>
       </c>
       <c r="D46">
-        <v>2941.731094064522</v>
+        <v>2947.884328318508</v>
       </c>
       <c r="E46">
-        <v>1208.596</v>
+        <v>1250.905</v>
       </c>
       <c r="F46">
-        <v>1861.596</v>
+        <v>1903.905</v>
       </c>
       <c r="G46">
         <v>1493.3</v>
@@ -5065,28 +5065,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M46">
-        <v>101.0846628</v>
+        <v>103.3820415</v>
       </c>
       <c r="N46">
-        <v>563.1922260888889</v>
+        <v>560.8948473888888</v>
       </c>
       <c r="O46">
-        <v>168.9576678266667</v>
+        <v>168.2684542166666</v>
       </c>
       <c r="P46">
-        <v>394.2345582622222</v>
+        <v>392.6263931722222</v>
       </c>
       <c r="Q46">
-        <v>394.8465582622222</v>
+        <v>393.2383931722222</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1331306548939624</v>
+        <v>0.1344111630302375</v>
       </c>
       <c r="T46">
-        <v>1.270767437873808</v>
+        <v>1.289400391508321</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.571490377360085</v>
+        <v>6.425457257863193</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09103063966663064</v>
+        <v>0.09078371259264231</v>
       </c>
       <c r="C47">
-        <v>2537.279328318508</v>
+        <v>2501.149358033279</v>
       </c>
       <c r="D47">
-        <v>2947.884328318508</v>
+        <v>2954.063358033279</v>
       </c>
       <c r="E47">
-        <v>1250.905</v>
+        <v>1293.214</v>
       </c>
       <c r="F47">
-        <v>1903.905</v>
+        <v>1946.214</v>
       </c>
       <c r="G47">
         <v>1493.3</v>
@@ -5147,28 +5147,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M47">
-        <v>103.3820415</v>
+        <v>105.6794202</v>
       </c>
       <c r="N47">
-        <v>560.8948473888888</v>
+        <v>558.5974686888889</v>
       </c>
       <c r="O47">
-        <v>168.2684542166666</v>
+        <v>167.5792406066666</v>
       </c>
       <c r="P47">
-        <v>392.6263931722222</v>
+        <v>391.0182280822222</v>
       </c>
       <c r="Q47">
-        <v>393.2383931722222</v>
+        <v>391.6302280822222</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1344111630302375</v>
+        <v>0.135739097393782</v>
       </c>
       <c r="T47">
-        <v>1.289400391508321</v>
+        <v>1.308723454536705</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.425457257863193</v>
+        <v>6.285773404431385</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09078371259264231</v>
+        <v>0.090536785518654</v>
       </c>
       <c r="C48">
-        <v>2501.149358033279</v>
+        <v>2465.045345758347</v>
       </c>
       <c r="D48">
-        <v>2954.063358033279</v>
+        <v>2960.268345758348</v>
       </c>
       <c r="E48">
-        <v>1293.214</v>
+        <v>1335.523</v>
       </c>
       <c r="F48">
-        <v>1946.214</v>
+        <v>1988.523</v>
       </c>
       <c r="G48">
         <v>1493.3</v>
@@ -5229,28 +5229,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M48">
-        <v>105.6794202</v>
+        <v>107.9767989</v>
       </c>
       <c r="N48">
-        <v>558.5974686888889</v>
+        <v>556.3000899888889</v>
       </c>
       <c r="O48">
-        <v>167.5792406066666</v>
+        <v>166.8900269966666</v>
       </c>
       <c r="P48">
-        <v>391.0182280822222</v>
+        <v>389.4100629922223</v>
       </c>
       <c r="Q48">
-        <v>391.6302280822222</v>
+        <v>390.0220629922223</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.135739097393782</v>
+        <v>0.1371171424880264</v>
       </c>
       <c r="T48">
-        <v>1.308723454536705</v>
+        <v>1.32877568975484</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.285773404431385</v>
+        <v>6.152033544762633</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.090536785518654</v>
+        <v>0.09062585844466567</v>
       </c>
       <c r="C49">
-        <v>2465.045345758347</v>
+        <v>2420.49504431886</v>
       </c>
       <c r="D49">
-        <v>2960.268345758348</v>
+        <v>2958.027044318859</v>
       </c>
       <c r="E49">
-        <v>1335.523</v>
+        <v>1377.832</v>
       </c>
       <c r="F49">
-        <v>1988.523</v>
+        <v>2030.832</v>
       </c>
       <c r="G49">
         <v>1493.3</v>
@@ -5311,45 +5311,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M49">
-        <v>107.9767989</v>
+        <v>112.3050096</v>
       </c>
       <c r="N49">
-        <v>556.3000899888889</v>
+        <v>551.9718792888889</v>
       </c>
       <c r="O49">
-        <v>166.8900269966666</v>
+        <v>165.5915637866667</v>
       </c>
       <c r="P49">
-        <v>389.4100629922223</v>
+        <v>386.3803155022222</v>
       </c>
       <c r="Q49">
-        <v>390.0220629922223</v>
+        <v>386.9923155022223</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1371171424880264</v>
+        <v>0.1385481893166648</v>
       </c>
       <c r="T49">
-        <v>1.32877568975484</v>
+        <v>1.349599164789057</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.152033544762633</v>
+        <v>5.914935506927635</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09062585844466567</v>
+        <v>0.09038593137067735</v>
       </c>
       <c r="C50">
-        <v>2420.49504431886</v>
+        <v>2384.230977058693</v>
       </c>
       <c r="D50">
-        <v>2958.027044318859</v>
+        <v>2964.071977058693</v>
       </c>
       <c r="E50">
-        <v>1377.832</v>
+        <v>1420.141</v>
       </c>
       <c r="F50">
-        <v>2030.832</v>
+        <v>2073.141</v>
       </c>
       <c r="G50">
         <v>1493.3</v>
@@ -5393,28 +5393,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M50">
-        <v>112.3050096</v>
+        <v>114.6446973</v>
       </c>
       <c r="N50">
-        <v>551.9718792888889</v>
+        <v>549.6321915888889</v>
       </c>
       <c r="O50">
-        <v>165.5915637866667</v>
+        <v>164.8896574766667</v>
       </c>
       <c r="P50">
-        <v>386.3803155022222</v>
+        <v>384.7425341122222</v>
       </c>
       <c r="Q50">
-        <v>386.9923155022223</v>
+        <v>385.3545341122222</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1385481893166648</v>
+        <v>0.1400353556287791</v>
       </c>
       <c r="T50">
-        <v>1.349599164789057</v>
+        <v>1.37123924668736</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.914935506927635</v>
+        <v>5.794222537398499</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09038593137067735</v>
+        <v>0.09014600429668905</v>
       </c>
       <c r="C51">
-        <v>2384.230977058693</v>
+        <v>2347.991666867131</v>
       </c>
       <c r="D51">
-        <v>2964.071977058693</v>
+        <v>2970.141666867131</v>
       </c>
       <c r="E51">
-        <v>1420.141</v>
+        <v>1462.45</v>
       </c>
       <c r="F51">
-        <v>2073.141</v>
+        <v>2115.45</v>
       </c>
       <c r="G51">
         <v>1493.3</v>
@@ -5475,28 +5475,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M51">
-        <v>114.6446973</v>
+        <v>116.984385</v>
       </c>
       <c r="N51">
-        <v>549.6321915888889</v>
+        <v>547.2925038888889</v>
       </c>
       <c r="O51">
-        <v>164.8896574766667</v>
+        <v>164.1877511666667</v>
       </c>
       <c r="P51">
-        <v>384.7425341122222</v>
+        <v>383.1047527222222</v>
       </c>
       <c r="Q51">
-        <v>385.3545341122222</v>
+        <v>383.7167527222222</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1400353556287791</v>
+        <v>0.1415820085933781</v>
       </c>
       <c r="T51">
-        <v>1.37123924668736</v>
+        <v>1.393744931861596</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.794222537398499</v>
+        <v>5.67833808665053</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09014600429668905</v>
+        <v>0.08990607722270073</v>
       </c>
       <c r="C52">
-        <v>2347.991666867131</v>
+        <v>2311.777266145404</v>
       </c>
       <c r="D52">
-        <v>2970.141666867131</v>
+        <v>2976.236266145404</v>
       </c>
       <c r="E52">
-        <v>1462.45</v>
+        <v>1504.759</v>
       </c>
       <c r="F52">
-        <v>2115.45</v>
+        <v>2157.759</v>
       </c>
       <c r="G52">
         <v>1493.3</v>
@@ -5557,28 +5557,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M52">
-        <v>116.984385</v>
+        <v>119.3240727</v>
       </c>
       <c r="N52">
-        <v>547.2925038888889</v>
+        <v>544.9528161888888</v>
       </c>
       <c r="O52">
-        <v>164.1877511666667</v>
+        <v>163.4858448566667</v>
       </c>
       <c r="P52">
-        <v>383.1047527222222</v>
+        <v>381.4669713322222</v>
       </c>
       <c r="Q52">
-        <v>383.7167527222222</v>
+        <v>382.0789713322222</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1415820085933781</v>
+        <v>0.1431917902504097</v>
       </c>
       <c r="T52">
-        <v>1.393744931861596</v>
+        <v>1.417169216430699</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.67833808665053</v>
+        <v>5.566998124167185</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08990607722270073</v>
+        <v>0.08966615014871243</v>
       </c>
       <c r="C53">
-        <v>2311.777266145404</v>
+        <v>2275.587928548192</v>
       </c>
       <c r="D53">
-        <v>2976.236266145404</v>
+        <v>2982.355928548192</v>
       </c>
       <c r="E53">
-        <v>1504.759</v>
+        <v>1547.068</v>
       </c>
       <c r="F53">
-        <v>2157.759</v>
+        <v>2200.068</v>
       </c>
       <c r="G53">
         <v>1493.3</v>
@@ -5639,28 +5639,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M53">
-        <v>119.3240727</v>
+        <v>121.6637604</v>
       </c>
       <c r="N53">
-        <v>544.9528161888888</v>
+        <v>542.6131284888888</v>
       </c>
       <c r="O53">
-        <v>163.4858448566667</v>
+        <v>162.7839385466666</v>
       </c>
       <c r="P53">
-        <v>381.4669713322222</v>
+        <v>379.8291899422222</v>
       </c>
       <c r="Q53">
-        <v>382.0789713322222</v>
+        <v>380.4411899422223</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1431917902504097</v>
+        <v>0.1448686461431509</v>
       </c>
       <c r="T53">
-        <v>1.417169216430699</v>
+        <v>1.441569512856847</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.566998124167185</v>
+        <v>5.459940467933201</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08966615014871243</v>
+        <v>0.08942622307472411</v>
       </c>
       <c r="C54">
-        <v>2275.587928548192</v>
+        <v>2239.423808996546</v>
       </c>
       <c r="D54">
-        <v>2982.355928548192</v>
+        <v>2988.500808996546</v>
       </c>
       <c r="E54">
-        <v>1547.068</v>
+        <v>1589.377</v>
       </c>
       <c r="F54">
-        <v>2200.068</v>
+        <v>2242.377</v>
       </c>
       <c r="G54">
         <v>1493.3</v>
@@ -5721,28 +5721,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M54">
-        <v>121.6637604</v>
+        <v>124.0034481</v>
       </c>
       <c r="N54">
-        <v>542.6131284888888</v>
+        <v>540.2734407888888</v>
       </c>
       <c r="O54">
-        <v>162.7839385466666</v>
+        <v>162.0820322366666</v>
       </c>
       <c r="P54">
-        <v>379.8291899422222</v>
+        <v>378.1914085522222</v>
       </c>
       <c r="Q54">
-        <v>380.4411899422223</v>
+        <v>378.8034085522222</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1448686461431509</v>
+        <v>0.146616857605796</v>
       </c>
       <c r="T54">
-        <v>1.441569512856847</v>
+        <v>1.467008119769214</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.459940467933201</v>
+        <v>5.356922723255216</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08942622307472411</v>
+        <v>0.0891862960007358</v>
       </c>
       <c r="C55">
-        <v>2239.423808996546</v>
+        <v>2203.285063690956</v>
       </c>
       <c r="D55">
-        <v>2988.500808996546</v>
+        <v>2994.671063690956</v>
       </c>
       <c r="E55">
-        <v>1589.377</v>
+        <v>1631.686</v>
       </c>
       <c r="F55">
-        <v>2242.377</v>
+        <v>2284.686</v>
       </c>
       <c r="G55">
         <v>1493.3</v>
@@ -5803,28 +5803,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M55">
-        <v>124.0034481</v>
+        <v>126.3431358</v>
       </c>
       <c r="N55">
-        <v>540.2734407888888</v>
+        <v>537.9337530888888</v>
       </c>
       <c r="O55">
-        <v>162.0820322366666</v>
+        <v>161.3801259266666</v>
       </c>
       <c r="P55">
-        <v>378.1914085522222</v>
+        <v>376.5536271622221</v>
       </c>
       <c r="Q55">
-        <v>378.8034085522222</v>
+        <v>377.1656271622222</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.146616857605796</v>
+        <v>0.1484410782624691</v>
       </c>
       <c r="T55">
-        <v>1.467008119769214</v>
+        <v>1.493552753069076</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.356922723255216</v>
+        <v>5.257720450602341</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0891862960007358</v>
+        <v>0.0889463689267475</v>
       </c>
       <c r="C56">
-        <v>2203.285063690956</v>
+        <v>2167.171850124588</v>
       </c>
       <c r="D56">
-        <v>2994.671063690956</v>
+        <v>3000.866850124588</v>
       </c>
       <c r="E56">
-        <v>1631.686</v>
+        <v>1673.995</v>
       </c>
       <c r="F56">
-        <v>2284.686</v>
+        <v>2326.995</v>
       </c>
       <c r="G56">
         <v>1493.3</v>
@@ -5885,28 +5885,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M56">
-        <v>126.3431358</v>
+        <v>128.6828235</v>
       </c>
       <c r="N56">
-        <v>537.9337530888888</v>
+        <v>535.5940653888888</v>
       </c>
       <c r="O56">
-        <v>161.3801259266666</v>
+        <v>160.6782196166666</v>
       </c>
       <c r="P56">
-        <v>376.5536271622221</v>
+        <v>374.9158457722222</v>
       </c>
       <c r="Q56">
-        <v>377.1656271622222</v>
+        <v>375.5278457722222</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1484410782624691</v>
+        <v>0.1503463753927722</v>
       </c>
       <c r="T56">
-        <v>1.493552753069076</v>
+        <v>1.521277147848932</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.257720450602341</v>
+        <v>5.162125533318662</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0889463689267475</v>
+        <v>0.08870644185275917</v>
       </c>
       <c r="C57">
-        <v>2167.171850124588</v>
+        <v>2131.084327096686</v>
       </c>
       <c r="D57">
-        <v>3000.866850124588</v>
+        <v>3007.088327096686</v>
       </c>
       <c r="E57">
-        <v>1673.995</v>
+        <v>1716.304</v>
       </c>
       <c r="F57">
-        <v>2326.995</v>
+        <v>2369.304</v>
       </c>
       <c r="G57">
         <v>1493.3</v>
@@ -5967,28 +5967,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M57">
-        <v>128.6828235</v>
+        <v>131.0225112</v>
       </c>
       <c r="N57">
-        <v>535.5940653888888</v>
+        <v>533.2543776888888</v>
       </c>
       <c r="O57">
-        <v>160.6782196166666</v>
+        <v>159.9763133066666</v>
       </c>
       <c r="P57">
-        <v>374.9158457722222</v>
+        <v>373.2780643822222</v>
       </c>
       <c r="Q57">
-        <v>375.5278457722222</v>
+        <v>373.8900643822222</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1503463753927722</v>
+        <v>0.152338276938089</v>
       </c>
       <c r="T57">
-        <v>1.521277147848932</v>
+        <v>1.550261742391508</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.162125533318662</v>
+        <v>5.069944720223686</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08870644185275917</v>
+        <v>0.08846651477877085</v>
       </c>
       <c r="C58">
-        <v>2131.084327096686</v>
+        <v>2095.022654726134</v>
       </c>
       <c r="D58">
-        <v>3007.088327096686</v>
+        <v>3013.335654726134</v>
       </c>
       <c r="E58">
-        <v>1716.304</v>
+        <v>1758.613</v>
       </c>
       <c r="F58">
-        <v>2369.304</v>
+        <v>2411.613</v>
       </c>
       <c r="G58">
         <v>1493.3</v>
@@ -6049,28 +6049,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M58">
-        <v>131.0225112</v>
+        <v>133.3621989</v>
       </c>
       <c r="N58">
-        <v>533.2543776888888</v>
+        <v>530.9146899888889</v>
       </c>
       <c r="O58">
-        <v>159.9763133066666</v>
+        <v>159.2744069966667</v>
       </c>
       <c r="P58">
-        <v>373.2780643822222</v>
+        <v>371.6402829922222</v>
       </c>
       <c r="Q58">
-        <v>373.8900643822222</v>
+        <v>372.2522829922222</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.152338276938089</v>
+        <v>0.154422825066909</v>
       </c>
       <c r="T58">
-        <v>1.550261742391508</v>
+        <v>1.580594457610483</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.069944720223686</v>
+        <v>4.980998321623272</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08846651477877085</v>
+        <v>0.08822658770478253</v>
       </c>
       <c r="C59">
-        <v>2095.022654726134</v>
+        <v>2058.986994465199</v>
       </c>
       <c r="D59">
-        <v>3013.335654726134</v>
+        <v>3019.608994465199</v>
       </c>
       <c r="E59">
-        <v>1758.613</v>
+        <v>1800.922</v>
       </c>
       <c r="F59">
-        <v>2411.613</v>
+        <v>2453.922</v>
       </c>
       <c r="G59">
         <v>1493.3</v>
@@ -6131,28 +6131,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M59">
-        <v>133.3621989</v>
+        <v>135.7018866</v>
       </c>
       <c r="N59">
-        <v>530.9146899888889</v>
+        <v>528.5750022888889</v>
       </c>
       <c r="O59">
-        <v>159.2744069966667</v>
+        <v>158.5725006866666</v>
       </c>
       <c r="P59">
-        <v>371.6402829922222</v>
+        <v>370.0025016022222</v>
       </c>
       <c r="Q59">
-        <v>372.2522829922222</v>
+        <v>370.6145016022222</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.154422825066909</v>
+        <v>0.1566066373923394</v>
       </c>
       <c r="T59">
-        <v>1.580594457610483</v>
+        <v>1.612371587839886</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.980998321623272</v>
+        <v>4.895119040215974</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08822658770478253</v>
+        <v>0.08798666063079422</v>
       </c>
       <c r="C60">
-        <v>2058.986994465199</v>
+        <v>2022.977509113434</v>
       </c>
       <c r="D60">
-        <v>3019.608994465199</v>
+        <v>3025.908509113434</v>
       </c>
       <c r="E60">
-        <v>1800.922</v>
+        <v>1843.231</v>
       </c>
       <c r="F60">
-        <v>2453.922</v>
+        <v>2496.231</v>
       </c>
       <c r="G60">
         <v>1493.3</v>
@@ -6213,28 +6213,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M60">
-        <v>135.7018866</v>
+        <v>138.0415743</v>
       </c>
       <c r="N60">
-        <v>528.5750022888889</v>
+        <v>526.2353145888889</v>
       </c>
       <c r="O60">
-        <v>158.5725006866666</v>
+        <v>157.8705943766666</v>
       </c>
       <c r="P60">
-        <v>370.0025016022222</v>
+        <v>368.3647202122222</v>
       </c>
       <c r="Q60">
-        <v>370.6145016022222</v>
+        <v>368.9767202122222</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1566066373923393</v>
+        <v>0.1588969771482786</v>
       </c>
       <c r="T60">
-        <v>1.612371587839885</v>
+        <v>1.645698821982917</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.895119040215974</v>
+        <v>4.81215092089028</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08798666063079422</v>
+        <v>0.08774673355680591</v>
       </c>
       <c r="C61">
-        <v>2022.977509113434</v>
+        <v>1986.994362831764</v>
       </c>
       <c r="D61">
-        <v>3025.908509113434</v>
+        <v>3032.234362831763</v>
       </c>
       <c r="E61">
-        <v>1843.231</v>
+        <v>1885.54</v>
       </c>
       <c r="F61">
-        <v>2496.231</v>
+        <v>2538.54</v>
       </c>
       <c r="G61">
         <v>1493.3</v>
@@ -6295,28 +6295,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M61">
-        <v>138.0415743</v>
+        <v>140.381262</v>
       </c>
       <c r="N61">
-        <v>526.2353145888889</v>
+        <v>523.8956268888888</v>
       </c>
       <c r="O61">
-        <v>157.8705943766666</v>
+        <v>157.1686880666666</v>
       </c>
       <c r="P61">
-        <v>368.3647202122222</v>
+        <v>366.7269388222222</v>
       </c>
       <c r="Q61">
-        <v>368.9767202122222</v>
+        <v>367.3389388222222</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1588969771482786</v>
+        <v>0.1613018338920148</v>
       </c>
       <c r="T61">
-        <v>1.645698821982917</v>
+        <v>1.680692417833101</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.81215092089028</v>
+        <v>4.731948405542108</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08774673355680591</v>
+        <v>0.0875068064828176</v>
       </c>
       <c r="C62">
-        <v>1986.994362831764</v>
+        <v>1951.037721156744</v>
       </c>
       <c r="D62">
-        <v>3032.234362831763</v>
+        <v>3038.586721156744</v>
       </c>
       <c r="E62">
-        <v>1885.54</v>
+        <v>1927.849</v>
       </c>
       <c r="F62">
-        <v>2538.54</v>
+        <v>2580.849</v>
       </c>
       <c r="G62">
         <v>1493.3</v>
@@ -6377,28 +6377,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M62">
-        <v>140.381262</v>
+        <v>142.7209497</v>
       </c>
       <c r="N62">
-        <v>523.8956268888888</v>
+        <v>521.5559391888888</v>
       </c>
       <c r="O62">
-        <v>157.1686880666666</v>
+        <v>156.4667817566666</v>
       </c>
       <c r="P62">
-        <v>366.7269388222222</v>
+        <v>365.0891574322222</v>
       </c>
       <c r="Q62">
-        <v>367.3389388222222</v>
+        <v>365.7011574322222</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1613018338920148</v>
+        <v>0.1638300166226092</v>
       </c>
       <c r="T62">
-        <v>1.680692417833101</v>
+        <v>1.717480557060217</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.731948405542108</v>
+        <v>4.65437548086109</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0875068064828176</v>
+        <v>0.08726687940882928</v>
       </c>
       <c r="C63">
-        <v>1951.037721156744</v>
+        <v>1915.107751015002</v>
       </c>
       <c r="D63">
-        <v>3038.586721156744</v>
+        <v>3044.965751015002</v>
       </c>
       <c r="E63">
-        <v>1927.849</v>
+        <v>1970.158</v>
       </c>
       <c r="F63">
-        <v>2580.849</v>
+        <v>2623.158</v>
       </c>
       <c r="G63">
         <v>1493.3</v>
@@ -6459,28 +6459,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M63">
-        <v>142.7209497</v>
+        <v>145.0606374</v>
       </c>
       <c r="N63">
-        <v>521.5559391888888</v>
+        <v>519.2162514888888</v>
       </c>
       <c r="O63">
-        <v>156.4667817566666</v>
+        <v>155.7648754466667</v>
       </c>
       <c r="P63">
-        <v>365.0891574322222</v>
+        <v>363.4513760422221</v>
       </c>
       <c r="Q63">
-        <v>365.7011574322222</v>
+        <v>364.0633760422222</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1638300166226092</v>
+        <v>0.1664912616021823</v>
       </c>
       <c r="T63">
-        <v>1.717480557060217</v>
+        <v>1.756204914141392</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.65437548086109</v>
+        <v>4.579304908589137</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08726687940882928</v>
+        <v>0.08702695233484097</v>
       </c>
       <c r="C64">
-        <v>1915.107751015002</v>
+        <v>1879.204620737859</v>
       </c>
       <c r="D64">
-        <v>3044.965751015002</v>
+        <v>3051.371620737858</v>
       </c>
       <c r="E64">
-        <v>1970.158</v>
+        <v>2012.467</v>
       </c>
       <c r="F64">
-        <v>2623.158</v>
+        <v>2665.467</v>
       </c>
       <c r="G64">
         <v>1493.3</v>
@@ -6541,28 +6541,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M64">
-        <v>145.0606374</v>
+        <v>147.4003251</v>
       </c>
       <c r="N64">
-        <v>519.2162514888888</v>
+        <v>516.8765637888889</v>
       </c>
       <c r="O64">
-        <v>155.7648754466667</v>
+        <v>155.0629691366667</v>
       </c>
       <c r="P64">
-        <v>363.4513760422221</v>
+        <v>361.8135946522223</v>
       </c>
       <c r="Q64">
-        <v>364.0633760422222</v>
+        <v>362.4255946522223</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1664912616021823</v>
+        <v>0.1692963576617323</v>
       </c>
       <c r="T64">
-        <v>1.756204914141392</v>
+        <v>1.797022479713441</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.579304908589137</v>
+        <v>4.506617529087722</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08702695233484097</v>
+        <v>0.08790702526085266</v>
       </c>
       <c r="C65">
-        <v>1879.204620737859</v>
+        <v>1813.529225765669</v>
       </c>
       <c r="D65">
-        <v>3051.371620737858</v>
+        <v>3028.005225765669</v>
       </c>
       <c r="E65">
-        <v>2012.467</v>
+        <v>2054.776</v>
       </c>
       <c r="F65">
-        <v>2665.467</v>
+        <v>2707.776</v>
       </c>
       <c r="G65">
         <v>1493.3</v>
@@ -6623,45 +6623,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M65">
-        <v>147.4003251</v>
+        <v>156.5094528</v>
       </c>
       <c r="N65">
-        <v>516.8765637888889</v>
+        <v>507.7674360888889</v>
       </c>
       <c r="O65">
-        <v>155.0629691366667</v>
+        <v>152.3302308266667</v>
       </c>
       <c r="P65">
-        <v>361.8135946522223</v>
+        <v>355.4372052622222</v>
       </c>
       <c r="Q65">
-        <v>362.4255946522223</v>
+        <v>356.0492052622222</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1692963576617323</v>
+        <v>0.1722572923912574</v>
       </c>
       <c r="T65">
-        <v>1.797022479713441</v>
+        <v>1.840107687817271</v>
       </c>
       <c r="U65">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.506617529087722</v>
+        <v>4.244324397055772</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08790702526085266</v>
+        <v>0.08768459818686433</v>
       </c>
       <c r="C66">
-        <v>1813.529225765669</v>
+        <v>1777.091921692493</v>
       </c>
       <c r="D66">
-        <v>3028.005225765669</v>
+        <v>3033.876921692493</v>
       </c>
       <c r="E66">
-        <v>2054.776</v>
+        <v>2097.085</v>
       </c>
       <c r="F66">
-        <v>2707.776</v>
+        <v>2750.085</v>
       </c>
       <c r="G66">
         <v>1493.3</v>
@@ -6705,28 +6705,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M66">
-        <v>156.5094528</v>
+        <v>158.954913</v>
       </c>
       <c r="N66">
-        <v>507.7674360888889</v>
+        <v>505.3219758888888</v>
       </c>
       <c r="O66">
-        <v>152.3302308266667</v>
+        <v>151.5965927666666</v>
       </c>
       <c r="P66">
-        <v>355.4372052622222</v>
+        <v>353.7253831222222</v>
       </c>
       <c r="Q66">
-        <v>356.0492052622222</v>
+        <v>354.3373831222222</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1722572923912574</v>
+        <v>0.175387423391041</v>
       </c>
       <c r="T66">
-        <v>1.840107687817271</v>
+        <v>1.885654907812747</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.244324397055772</v>
+        <v>4.179027098639529</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08768459818686433</v>
+        <v>0.08746217111287603</v>
       </c>
       <c r="C67">
-        <v>1777.091921692493</v>
+        <v>1740.677433826951</v>
       </c>
       <c r="D67">
-        <v>3033.876921692493</v>
+        <v>3039.771433826951</v>
       </c>
       <c r="E67">
-        <v>2097.085</v>
+        <v>2139.394</v>
       </c>
       <c r="F67">
-        <v>2750.085</v>
+        <v>2792.394</v>
       </c>
       <c r="G67">
         <v>1493.3</v>
@@ -6787,28 +6787,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M67">
-        <v>158.954913</v>
+        <v>161.4003732</v>
       </c>
       <c r="N67">
-        <v>505.3219758888888</v>
+        <v>502.8765156888888</v>
       </c>
       <c r="O67">
-        <v>151.5965927666666</v>
+        <v>150.8629547066666</v>
       </c>
       <c r="P67">
-        <v>353.7253831222222</v>
+        <v>352.0135609822222</v>
       </c>
       <c r="Q67">
-        <v>354.3373831222222</v>
+        <v>352.6255609822222</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.175387423391041</v>
+        <v>0.178701679743753</v>
       </c>
       <c r="T67">
-        <v>1.885654907812747</v>
+        <v>1.933881376043253</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.179027098639529</v>
+        <v>4.115708506235901</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08746217111287603</v>
+        <v>0.08723974403888771</v>
       </c>
       <c r="C68">
-        <v>1740.677433826951</v>
+        <v>1704.285895416594</v>
       </c>
       <c r="D68">
-        <v>3039.771433826951</v>
+        <v>3045.688895416595</v>
       </c>
       <c r="E68">
-        <v>2139.394</v>
+        <v>2181.703</v>
       </c>
       <c r="F68">
-        <v>2792.394</v>
+        <v>2834.703</v>
       </c>
       <c r="G68">
         <v>1493.3</v>
@@ -6869,28 +6869,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M68">
-        <v>161.4003732</v>
+        <v>163.8458334</v>
       </c>
       <c r="N68">
-        <v>502.8765156888888</v>
+        <v>500.4310554888888</v>
       </c>
       <c r="O68">
-        <v>150.8629547066666</v>
+        <v>150.1293166466666</v>
       </c>
       <c r="P68">
-        <v>352.0135609822222</v>
+        <v>350.3017388422222</v>
       </c>
       <c r="Q68">
-        <v>352.6255609822222</v>
+        <v>350.9137388422222</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.178701679743753</v>
+        <v>0.1822168001178416</v>
       </c>
       <c r="T68">
-        <v>1.933881376043253</v>
+        <v>1.985030660530152</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.115708506235901</v>
+        <v>4.0542800210682</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08723974403888771</v>
+        <v>0.08868331696489939</v>
       </c>
       <c r="C69">
-        <v>1704.285895416594</v>
+        <v>1623.97733492043</v>
       </c>
       <c r="D69">
-        <v>3045.688895416595</v>
+        <v>3007.689334920431</v>
       </c>
       <c r="E69">
-        <v>2181.703</v>
+        <v>2224.012</v>
       </c>
       <c r="F69">
-        <v>2834.703</v>
+        <v>2877.012</v>
       </c>
       <c r="G69">
         <v>1493.3</v>
@@ -6951,45 +6951,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M69">
-        <v>163.8458334</v>
+        <v>176.3608356</v>
       </c>
       <c r="N69">
-        <v>500.4310554888888</v>
+        <v>487.9160532888889</v>
       </c>
       <c r="O69">
-        <v>150.1293166466666</v>
+        <v>146.3748159866666</v>
       </c>
       <c r="P69">
-        <v>350.3017388422222</v>
+        <v>341.5412373022222</v>
       </c>
       <c r="Q69">
-        <v>350.9137388422222</v>
+        <v>342.1532373022222</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1822168001178416</v>
+        <v>0.1859516155153106</v>
       </c>
       <c r="T69">
-        <v>1.985030660530152</v>
+        <v>2.039376775297483</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.0542800210682</v>
+        <v>3.766578257746069</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08868331696489939</v>
+        <v>0.08848538989091109</v>
       </c>
       <c r="C70">
-        <v>1623.97733492043</v>
+        <v>1586.822235597361</v>
       </c>
       <c r="D70">
-        <v>3007.689334920431</v>
+        <v>3012.843235597361</v>
       </c>
       <c r="E70">
-        <v>2224.012</v>
+        <v>2266.321</v>
       </c>
       <c r="F70">
-        <v>2877.012</v>
+        <v>2919.321</v>
       </c>
       <c r="G70">
         <v>1493.3</v>
@@ -7033,28 +7033,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M70">
-        <v>176.3608356</v>
+        <v>178.9543773</v>
       </c>
       <c r="N70">
-        <v>487.9160532888889</v>
+        <v>485.3225115888888</v>
       </c>
       <c r="O70">
-        <v>146.3748159866666</v>
+        <v>145.5967534766666</v>
       </c>
       <c r="P70">
-        <v>341.5412373022222</v>
+        <v>339.7257581122221</v>
       </c>
       <c r="Q70">
-        <v>342.1532373022222</v>
+        <v>340.3377581122222</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1859516155153106</v>
+        <v>0.1899273867448745</v>
       </c>
       <c r="T70">
-        <v>2.039376775297483</v>
+        <v>2.097229091017544</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.766578257746069</v>
+        <v>3.711990167054096</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08848538989091109</v>
+        <v>0.08828746281692276</v>
       </c>
       <c r="C71">
-        <v>1586.822235597361</v>
+        <v>1549.684829782174</v>
       </c>
       <c r="D71">
-        <v>3012.843235597361</v>
+        <v>3018.014829782175</v>
       </c>
       <c r="E71">
-        <v>2266.321</v>
+        <v>2308.63</v>
       </c>
       <c r="F71">
-        <v>2919.321</v>
+        <v>2961.63</v>
       </c>
       <c r="G71">
         <v>1493.3</v>
@@ -7115,28 +7115,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M71">
-        <v>178.9543773</v>
+        <v>181.547919</v>
       </c>
       <c r="N71">
-        <v>485.3225115888888</v>
+        <v>482.7289698888889</v>
       </c>
       <c r="O71">
-        <v>145.5967534766666</v>
+        <v>144.8186909666667</v>
       </c>
       <c r="P71">
-        <v>339.7257581122221</v>
+        <v>337.9102789222222</v>
       </c>
       <c r="Q71">
-        <v>340.3377581122222</v>
+        <v>338.5222789222223</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1899273867448745</v>
+        <v>0.1941682093897426</v>
       </c>
       <c r="T71">
-        <v>2.097229091017544</v>
+        <v>2.15893822778561</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.711990167054096</v>
+        <v>3.658961736096181</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08828746281692276</v>
+        <v>0.08808953574293445</v>
       </c>
       <c r="C72">
-        <v>1549.684829782174</v>
+        <v>1512.565208745117</v>
       </c>
       <c r="D72">
-        <v>3018.014829782175</v>
+        <v>3023.204208745117</v>
       </c>
       <c r="E72">
-        <v>2308.63</v>
+        <v>2350.939</v>
       </c>
       <c r="F72">
-        <v>2961.63</v>
+        <v>3003.939</v>
       </c>
       <c r="G72">
         <v>1493.3</v>
@@ -7197,28 +7197,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M72">
-        <v>181.547919</v>
+        <v>184.1414607</v>
       </c>
       <c r="N72">
-        <v>482.7289698888889</v>
+        <v>480.1354281888889</v>
       </c>
       <c r="O72">
-        <v>144.8186909666667</v>
+        <v>144.0406284566666</v>
       </c>
       <c r="P72">
-        <v>337.9102789222222</v>
+        <v>336.0947997322222</v>
       </c>
       <c r="Q72">
-        <v>338.5222789222223</v>
+        <v>336.7067997322222</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1941682093897426</v>
+        <v>0.198701502561843</v>
       </c>
       <c r="T72">
-        <v>2.15893822778561</v>
+        <v>2.224903167089404</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.658961736096181</v>
+        <v>3.607427063756798</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08808953574293446</v>
+        <v>0.08789160866894613</v>
       </c>
       <c r="C73">
-        <v>1512.565208745116</v>
+        <v>1475.463464385258</v>
       </c>
       <c r="D73">
-        <v>3023.204208745116</v>
+        <v>3028.411464385258</v>
       </c>
       <c r="E73">
-        <v>2350.938999999999</v>
+        <v>2393.248</v>
       </c>
       <c r="F73">
-        <v>3003.938999999999</v>
+        <v>3046.248</v>
       </c>
       <c r="G73">
         <v>1493.3</v>
@@ -7279,28 +7279,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M73">
-        <v>184.1414607</v>
+        <v>186.7350024</v>
       </c>
       <c r="N73">
-        <v>480.1354281888889</v>
+        <v>477.5418864888888</v>
       </c>
       <c r="O73">
-        <v>144.0406284566667</v>
+        <v>143.2625659466667</v>
       </c>
       <c r="P73">
-        <v>336.0947997322222</v>
+        <v>334.2793205422222</v>
       </c>
       <c r="Q73">
-        <v>336.7067997322222</v>
+        <v>334.8913205422222</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1987015025618429</v>
+        <v>0.2035586023890933</v>
       </c>
       <c r="T73">
-        <v>2.224903167089403</v>
+        <v>2.29557988777204</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.607427063756799</v>
+        <v>3.55732391009351</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08789160866894613</v>
+        <v>0.08769368159495783</v>
       </c>
       <c r="C74">
-        <v>1475.463464385258</v>
+        <v>1438.37968923592</v>
       </c>
       <c r="D74">
-        <v>3028.411464385258</v>
+        <v>3033.63668923592</v>
       </c>
       <c r="E74">
-        <v>2393.248</v>
+        <v>2435.557</v>
       </c>
       <c r="F74">
-        <v>3046.248</v>
+        <v>3088.557</v>
       </c>
       <c r="G74">
         <v>1493.3</v>
@@ -7361,28 +7361,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M74">
-        <v>186.7350024</v>
+        <v>189.3285441</v>
       </c>
       <c r="N74">
-        <v>477.5418864888888</v>
+        <v>474.9483447888888</v>
       </c>
       <c r="O74">
-        <v>143.2625659466667</v>
+        <v>142.4845034366666</v>
       </c>
       <c r="P74">
-        <v>334.2793205422222</v>
+        <v>332.4638413522222</v>
       </c>
       <c r="Q74">
-        <v>334.8913205422222</v>
+        <v>333.0758413522222</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2035586023890933</v>
+        <v>0.2087754873887327</v>
       </c>
       <c r="T74">
-        <v>2.29557988777204</v>
+        <v>2.371491921097835</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.55732391009351</v>
+        <v>3.508593445571681</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08769368159495783</v>
+        <v>0.0889461545209695</v>
       </c>
       <c r="C75">
-        <v>1438.37968923592</v>
+        <v>1363.306398324095</v>
       </c>
       <c r="D75">
-        <v>3033.63668923592</v>
+        <v>3000.872398324095</v>
       </c>
       <c r="E75">
-        <v>2435.557</v>
+        <v>2477.866</v>
       </c>
       <c r="F75">
-        <v>3088.557</v>
+        <v>3130.866</v>
       </c>
       <c r="G75">
         <v>1493.3</v>
@@ -7443,45 +7443,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M75">
-        <v>189.3285441</v>
+        <v>200.6885106</v>
       </c>
       <c r="N75">
-        <v>474.9483447888888</v>
+        <v>463.5883782888889</v>
       </c>
       <c r="O75">
-        <v>142.4845034366666</v>
+        <v>139.0765134866666</v>
       </c>
       <c r="P75">
-        <v>332.4638413522222</v>
+        <v>324.5118648022222</v>
       </c>
       <c r="Q75">
-        <v>333.0758413522222</v>
+        <v>325.1238648022223</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2087754873887327</v>
+        <v>0.2143936712344981</v>
       </c>
       <c r="T75">
-        <v>2.371491921097835</v>
+        <v>2.453243341602537</v>
       </c>
       <c r="U75">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.3</v>
       </c>
       <c r="W75">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.508593445571681</v>
+        <v>3.309989629714702</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0889461545209695</v>
+        <v>0.0887678274469812</v>
       </c>
       <c r="C76">
-        <v>1363.306398324095</v>
+        <v>1325.619101203835</v>
       </c>
       <c r="D76">
-        <v>3000.872398324095</v>
+        <v>3005.494101203834</v>
       </c>
       <c r="E76">
-        <v>2477.866</v>
+        <v>2520.175</v>
       </c>
       <c r="F76">
-        <v>3130.866</v>
+        <v>3173.175</v>
       </c>
       <c r="G76">
         <v>1493.3</v>
@@ -7525,28 +7525,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M76">
-        <v>200.6885106</v>
+        <v>203.4005175</v>
       </c>
       <c r="N76">
-        <v>463.5883782888889</v>
+        <v>460.8763713888889</v>
       </c>
       <c r="O76">
-        <v>139.0765134866666</v>
+        <v>138.2629114166666</v>
       </c>
       <c r="P76">
-        <v>324.5118648022222</v>
+        <v>322.6134599722222</v>
       </c>
       <c r="Q76">
-        <v>325.1238648022223</v>
+        <v>323.2254599722223</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2143936712344981</v>
+        <v>0.2204613097879248</v>
       </c>
       <c r="T76">
-        <v>2.453243341602537</v>
+        <v>2.541534875747616</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.309989629714702</v>
+        <v>3.265856434651838</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0887678274469812</v>
+        <v>0.08858950037299287</v>
       </c>
       <c r="C77">
-        <v>1325.619101203835</v>
+        <v>1287.94606199433</v>
       </c>
       <c r="D77">
-        <v>3005.494101203834</v>
+        <v>3010.13006199433</v>
       </c>
       <c r="E77">
-        <v>2520.175</v>
+        <v>2562.484</v>
       </c>
       <c r="F77">
-        <v>3173.175</v>
+        <v>3215.484</v>
       </c>
       <c r="G77">
         <v>1493.3</v>
@@ -7607,28 +7607,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M77">
-        <v>203.4005175</v>
+        <v>206.1125244</v>
       </c>
       <c r="N77">
-        <v>460.8763713888889</v>
+        <v>458.1643644888889</v>
       </c>
       <c r="O77">
-        <v>138.2629114166666</v>
+        <v>137.4493093466666</v>
       </c>
       <c r="P77">
-        <v>322.6134599722222</v>
+        <v>320.7150551422222</v>
       </c>
       <c r="Q77">
-        <v>323.2254599722223</v>
+        <v>321.3270551422223</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2204613097879248</v>
+        <v>0.2270345848874704</v>
       </c>
       <c r="T77">
-        <v>2.541534875747616</v>
+        <v>2.637184037738118</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.265856434651838</v>
+        <v>3.222884639459051</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08858950037299287</v>
+        <v>0.08841117329900455</v>
       </c>
       <c r="C78">
-        <v>1287.94606199433</v>
+        <v>1250.287346775795</v>
       </c>
       <c r="D78">
-        <v>3010.13006199433</v>
+        <v>3014.780346775794</v>
       </c>
       <c r="E78">
-        <v>2562.484</v>
+        <v>2604.793</v>
       </c>
       <c r="F78">
-        <v>3215.484</v>
+        <v>3257.793</v>
       </c>
       <c r="G78">
         <v>1493.3</v>
@@ -7689,28 +7689,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M78">
-        <v>206.1125244</v>
+        <v>208.8245313</v>
       </c>
       <c r="N78">
-        <v>458.1643644888889</v>
+        <v>455.4523575888888</v>
       </c>
       <c r="O78">
-        <v>137.4493093466666</v>
+        <v>136.6357072766666</v>
       </c>
       <c r="P78">
-        <v>320.7150551422222</v>
+        <v>318.8166503122222</v>
       </c>
       <c r="Q78">
-        <v>321.3270551422223</v>
+        <v>319.4286503122223</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2270345848874704</v>
+        <v>0.2341794491261068</v>
       </c>
       <c r="T78">
-        <v>2.637184037738118</v>
+        <v>2.741150518162576</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.222884639459051</v>
+        <v>3.181028994790752</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08841117329900455</v>
+        <v>0.08823284622501626</v>
       </c>
       <c r="C79">
-        <v>1250.287346775795</v>
+        <v>1212.643022037415</v>
       </c>
       <c r="D79">
-        <v>3014.780346775794</v>
+        <v>3019.445022037415</v>
       </c>
       <c r="E79">
-        <v>2604.793</v>
+        <v>2647.102</v>
       </c>
       <c r="F79">
-        <v>3257.793</v>
+        <v>3300.102</v>
       </c>
       <c r="G79">
         <v>1493.3</v>
@@ -7771,28 +7771,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M79">
-        <v>208.8245313</v>
+        <v>211.5365382</v>
       </c>
       <c r="N79">
-        <v>455.4523575888888</v>
+        <v>452.7403506888888</v>
       </c>
       <c r="O79">
-        <v>136.6357072766666</v>
+        <v>135.8221052066666</v>
       </c>
       <c r="P79">
-        <v>318.8166503122222</v>
+        <v>316.9182454822222</v>
       </c>
       <c r="Q79">
-        <v>319.4286503122223</v>
+        <v>317.5302454822223</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2341794491261068</v>
+        <v>0.2419738464773466</v>
       </c>
       <c r="T79">
-        <v>2.741150518162576</v>
+        <v>2.85456849680744</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.181028994790752</v>
+        <v>3.140246571780614</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08823284622501626</v>
+        <v>0.08805451915102794</v>
       </c>
       <c r="C80">
-        <v>1212.643022037415</v>
+        <v>1175.013154680527</v>
       </c>
       <c r="D80">
-        <v>3019.445022037415</v>
+        <v>3024.124154680527</v>
       </c>
       <c r="E80">
-        <v>2647.102</v>
+        <v>2689.411</v>
       </c>
       <c r="F80">
-        <v>3300.102</v>
+        <v>3342.411</v>
       </c>
       <c r="G80">
         <v>1493.3</v>
@@ -7853,28 +7853,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M80">
-        <v>211.5365382</v>
+        <v>214.2485451</v>
       </c>
       <c r="N80">
-        <v>452.7403506888888</v>
+        <v>450.0283437888888</v>
       </c>
       <c r="O80">
-        <v>135.8221052066666</v>
+        <v>135.0085031366666</v>
       </c>
       <c r="P80">
-        <v>316.9182454822222</v>
+        <v>315.0198406522222</v>
       </c>
       <c r="Q80">
-        <v>317.5302454822223</v>
+        <v>315.6318406522223</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2419738464773466</v>
+        <v>0.2505105673858474</v>
       </c>
       <c r="T80">
-        <v>2.85456849680744</v>
+        <v>2.978788187704196</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.140246571780614</v>
+        <v>3.100496615175795</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08805451915102794</v>
+        <v>0.08787619207703962</v>
       </c>
       <c r="C81">
-        <v>1175.013154680527</v>
+        <v>1137.397812021804</v>
       </c>
       <c r="D81">
-        <v>3024.124154680527</v>
+        <v>3028.817812021804</v>
       </c>
       <c r="E81">
-        <v>2689.411</v>
+        <v>2731.72</v>
       </c>
       <c r="F81">
-        <v>3342.411</v>
+        <v>3384.72</v>
       </c>
       <c r="G81">
         <v>1493.3</v>
@@ -7935,28 +7935,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M81">
-        <v>214.2485451</v>
+        <v>216.960552</v>
       </c>
       <c r="N81">
-        <v>450.0283437888888</v>
+        <v>447.3163368888888</v>
       </c>
       <c r="O81">
-        <v>135.0085031366666</v>
+        <v>134.1949010666666</v>
       </c>
       <c r="P81">
-        <v>315.0198406522222</v>
+        <v>313.1214358222222</v>
       </c>
       <c r="Q81">
-        <v>315.6318406522223</v>
+        <v>313.7334358222222</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2505105673858474</v>
+        <v>0.2599009603851982</v>
       </c>
       <c r="T81">
-        <v>2.978788187704196</v>
+        <v>3.115429847690627</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.100496615175795</v>
+        <v>3.061740407486098</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08787619207703962</v>
+        <v>0.08769786500305131</v>
       </c>
       <c r="C82">
-        <v>1137.397812021804</v>
+        <v>1099.797061796493</v>
       </c>
       <c r="D82">
-        <v>3028.817812021804</v>
+        <v>3033.526061796493</v>
       </c>
       <c r="E82">
-        <v>2731.72</v>
+        <v>2774.029</v>
       </c>
       <c r="F82">
-        <v>3384.72</v>
+        <v>3427.029</v>
       </c>
       <c r="G82">
         <v>1493.3</v>
@@ -8017,28 +8017,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M82">
-        <v>216.960552</v>
+        <v>219.6725589</v>
       </c>
       <c r="N82">
-        <v>447.3163368888888</v>
+        <v>444.6043299888888</v>
       </c>
       <c r="O82">
-        <v>134.1949010666666</v>
+        <v>133.3812989966666</v>
       </c>
       <c r="P82">
-        <v>313.1214358222222</v>
+        <v>311.2230309922222</v>
       </c>
       <c r="Q82">
-        <v>313.7334358222222</v>
+        <v>311.8350309922222</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2599009603851982</v>
+        <v>0.2702798158055333</v>
       </c>
       <c r="T82">
-        <v>3.115429847690627</v>
+        <v>3.266454840307209</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.061740407486098</v>
+        <v>3.023941143196146</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08769786500305131</v>
+        <v>0.091996737929063</v>
       </c>
       <c r="C83">
-        <v>1099.797061796493</v>
+        <v>947.9173691753458</v>
       </c>
       <c r="D83">
-        <v>3033.526061796493</v>
+        <v>2923.955369175345</v>
       </c>
       <c r="E83">
-        <v>2774.029</v>
+        <v>2816.338</v>
       </c>
       <c r="F83">
-        <v>3427.029</v>
+        <v>3469.338</v>
       </c>
       <c r="G83">
         <v>1493.3</v>
@@ -8099,45 +8099,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M83">
-        <v>219.6725589</v>
+        <v>249.4454022</v>
       </c>
       <c r="N83">
-        <v>444.6043299888888</v>
+        <v>414.8314866888888</v>
       </c>
       <c r="O83">
-        <v>133.3812989966666</v>
+        <v>124.4494460066666</v>
       </c>
       <c r="P83">
-        <v>311.2230309922222</v>
+        <v>290.3820406822222</v>
       </c>
       <c r="Q83">
-        <v>311.8350309922222</v>
+        <v>290.9940406822222</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2702798158055333</v>
+        <v>0.2818118773836834</v>
       </c>
       <c r="T83">
-        <v>3.266454840307209</v>
+        <v>3.434260387658966</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.3</v>
       </c>
       <c r="W83">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.023941143196146</v>
+        <v>2.663015164962976</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.091996737929063</v>
+        <v>0.09187301085507468</v>
       </c>
       <c r="C84">
-        <v>947.9173691753458</v>
+        <v>908.6512102368806</v>
       </c>
       <c r="D84">
-        <v>2923.955369175345</v>
+        <v>2926.998210236881</v>
       </c>
       <c r="E84">
-        <v>2816.338</v>
+        <v>2858.647</v>
       </c>
       <c r="F84">
-        <v>3469.338</v>
+        <v>3511.647</v>
       </c>
       <c r="G84">
         <v>1493.3</v>
@@ -8181,28 +8181,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M84">
-        <v>249.4454022</v>
+        <v>252.4874193</v>
       </c>
       <c r="N84">
-        <v>414.8314866888888</v>
+        <v>411.7894695888888</v>
       </c>
       <c r="O84">
-        <v>124.4494460066666</v>
+        <v>123.5368408766666</v>
       </c>
       <c r="P84">
-        <v>290.3820406822222</v>
+        <v>288.2526287122221</v>
       </c>
       <c r="Q84">
-        <v>290.9940406822222</v>
+        <v>288.8646287122222</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2818118773836834</v>
+        <v>0.2947006520886747</v>
       </c>
       <c r="T84">
-        <v>3.434260387658966</v>
+        <v>3.621807764110931</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.663015164962976</v>
+        <v>2.63093064490318</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09187301085507468</v>
+        <v>0.09174928378108638</v>
       </c>
       <c r="C85">
-        <v>908.6512102368806</v>
+        <v>869.391391017004</v>
       </c>
       <c r="D85">
-        <v>2926.998210236881</v>
+        <v>2930.047391017004</v>
       </c>
       <c r="E85">
-        <v>2858.647</v>
+        <v>2900.956</v>
       </c>
       <c r="F85">
-        <v>3511.647</v>
+        <v>3553.956</v>
       </c>
       <c r="G85">
         <v>1493.3</v>
@@ -8263,28 +8263,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M85">
-        <v>252.4874193</v>
+        <v>255.5294364</v>
       </c>
       <c r="N85">
-        <v>411.7894695888888</v>
+        <v>408.7474524888888</v>
       </c>
       <c r="O85">
-        <v>123.5368408766666</v>
+        <v>122.6242357466666</v>
       </c>
       <c r="P85">
-        <v>288.2526287122221</v>
+        <v>286.1232167422222</v>
       </c>
       <c r="Q85">
-        <v>288.8646287122222</v>
+        <v>286.7352167422222</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2947006520886747</v>
+        <v>0.30920052363179</v>
       </c>
       <c r="T85">
-        <v>3.621807764110931</v>
+        <v>3.832798562619391</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.63093064490318</v>
+        <v>2.599610041987666</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09174928378108638</v>
+        <v>0.09162555670709806</v>
       </c>
       <c r="C86">
-        <v>869.3913910170045</v>
+        <v>830.1379313494581</v>
       </c>
       <c r="D86">
-        <v>2930.047391017004</v>
+        <v>2933.102931349458</v>
       </c>
       <c r="E86">
-        <v>2900.956</v>
+        <v>2943.264999999999</v>
       </c>
       <c r="F86">
-        <v>3553.956</v>
+        <v>3596.264999999999</v>
       </c>
       <c r="G86">
         <v>1493.3</v>
@@ -8345,28 +8345,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M86">
-        <v>255.5294364</v>
+        <v>258.5714535</v>
       </c>
       <c r="N86">
-        <v>408.7474524888888</v>
+        <v>405.7054353888889</v>
       </c>
       <c r="O86">
-        <v>122.6242357466666</v>
+        <v>121.7116306166667</v>
       </c>
       <c r="P86">
-        <v>286.1232167422222</v>
+        <v>283.9938047722222</v>
       </c>
       <c r="Q86">
-        <v>286.7352167422222</v>
+        <v>284.6058047722223</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3092005236317897</v>
+        <v>0.3256337113806537</v>
       </c>
       <c r="T86">
-        <v>3.832798562619388</v>
+        <v>4.071921467595643</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.599610041987667</v>
+        <v>2.569026394434871</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09162555670709806</v>
+        <v>0.09150182963310974</v>
       </c>
       <c r="C87">
-        <v>830.1379313494581</v>
+        <v>790.8908511507998</v>
       </c>
       <c r="D87">
-        <v>2933.102931349458</v>
+        <v>2936.164851150799</v>
       </c>
       <c r="E87">
-        <v>2943.264999999999</v>
+        <v>2985.574</v>
       </c>
       <c r="F87">
-        <v>3596.264999999999</v>
+        <v>3638.574</v>
       </c>
       <c r="G87">
         <v>1493.3</v>
@@ -8427,28 +8427,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M87">
-        <v>258.5714535</v>
+        <v>261.6134706</v>
       </c>
       <c r="N87">
-        <v>405.7054353888889</v>
+        <v>402.6634182888889</v>
       </c>
       <c r="O87">
-        <v>121.7116306166667</v>
+        <v>120.7990254866667</v>
       </c>
       <c r="P87">
-        <v>283.9938047722222</v>
+        <v>281.8643928022222</v>
       </c>
       <c r="Q87">
-        <v>284.6058047722223</v>
+        <v>282.4763928022222</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3256337113806537</v>
+        <v>0.3444144973793553</v>
       </c>
       <c r="T87">
-        <v>4.071921467595643</v>
+        <v>4.345204787568504</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.569026394434871</v>
+        <v>2.539153994499582</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09150182963310974</v>
+        <v>0.09137810255912143</v>
       </c>
       <c r="C88">
-        <v>790.8908511507998</v>
+        <v>751.6501704208395</v>
       </c>
       <c r="D88">
-        <v>2936.164851150799</v>
+        <v>2939.233170420839</v>
       </c>
       <c r="E88">
-        <v>2985.574</v>
+        <v>3027.883</v>
       </c>
       <c r="F88">
-        <v>3638.574</v>
+        <v>3680.883</v>
       </c>
       <c r="G88">
         <v>1493.3</v>
@@ -8509,28 +8509,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M88">
-        <v>261.6134706</v>
+        <v>264.6554877</v>
       </c>
       <c r="N88">
-        <v>402.6634182888889</v>
+        <v>399.6214011888889</v>
       </c>
       <c r="O88">
-        <v>120.7990254866667</v>
+        <v>119.8864203566666</v>
       </c>
       <c r="P88">
-        <v>281.8643928022222</v>
+        <v>279.7349808322222</v>
       </c>
       <c r="Q88">
-        <v>282.4763928022222</v>
+        <v>280.3469808322222</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3444144973793553</v>
+        <v>0.3660846350701648</v>
       </c>
       <c r="T88">
-        <v>4.345204787568504</v>
+        <v>4.6605316952295</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.539153994499582</v>
+        <v>2.509968316401885</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09137810255912143</v>
+        <v>0.09365677548513311</v>
       </c>
       <c r="C89">
-        <v>751.6501704208395</v>
+        <v>653.8412391449388</v>
       </c>
       <c r="D89">
-        <v>2939.233170420839</v>
+        <v>2883.733239144938</v>
       </c>
       <c r="E89">
-        <v>3027.883</v>
+        <v>3070.192</v>
       </c>
       <c r="F89">
-        <v>3680.883</v>
+        <v>3723.192</v>
       </c>
       <c r="G89">
         <v>1493.3</v>
@@ -8591,45 +8591,45 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M89">
-        <v>264.6554877</v>
+        <v>282.2179536</v>
       </c>
       <c r="N89">
-        <v>399.6214011888889</v>
+        <v>382.0589352888888</v>
       </c>
       <c r="O89">
-        <v>119.8864203566666</v>
+        <v>114.6176805866667</v>
       </c>
       <c r="P89">
-        <v>279.7349808322222</v>
+        <v>267.4412547022222</v>
       </c>
       <c r="Q89">
-        <v>280.3469808322222</v>
+        <v>268.0532547022222</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3660846350701648</v>
+        <v>0.3913664623761093</v>
       </c>
       <c r="T89">
-        <v>4.6605316952295</v>
+        <v>5.028413087500661</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.3</v>
       </c>
       <c r="W89">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.509968316401885</v>
+        <v>2.353772608777391</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09365677548513311</v>
+        <v>0.0935603484111448</v>
       </c>
       <c r="C90">
-        <v>653.8412391449388</v>
+        <v>613.8383365530549</v>
       </c>
       <c r="D90">
-        <v>2883.733239144938</v>
+        <v>2886.039336553055</v>
       </c>
       <c r="E90">
-        <v>3070.192</v>
+        <v>3112.501</v>
       </c>
       <c r="F90">
-        <v>3723.192</v>
+        <v>3765.501</v>
       </c>
       <c r="G90">
         <v>1493.3</v>
@@ -8673,28 +8673,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M90">
-        <v>282.2179536</v>
+        <v>285.4249758</v>
       </c>
       <c r="N90">
-        <v>382.0589352888888</v>
+        <v>378.8519130888888</v>
       </c>
       <c r="O90">
-        <v>114.6176805866667</v>
+        <v>113.6555739266666</v>
       </c>
       <c r="P90">
-        <v>267.4412547022222</v>
+        <v>265.1963391622222</v>
       </c>
       <c r="Q90">
-        <v>268.0532547022222</v>
+        <v>265.8083391622222</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3913664623761093</v>
+        <v>0.4212449855558618</v>
       </c>
       <c r="T90">
-        <v>5.028413087500661</v>
+        <v>5.463182005639305</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.353772608777391</v>
+        <v>2.327325725532702</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0935603484111448</v>
+        <v>0.09346392133715647</v>
       </c>
       <c r="C91">
-        <v>613.8383365530549</v>
+        <v>573.8391252467704</v>
       </c>
       <c r="D91">
-        <v>2886.039336553055</v>
+        <v>2888.34912524677</v>
       </c>
       <c r="E91">
-        <v>3112.501</v>
+        <v>3154.81</v>
       </c>
       <c r="F91">
-        <v>3765.501</v>
+        <v>3807.81</v>
       </c>
       <c r="G91">
         <v>1493.3</v>
@@ -8755,28 +8755,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M91">
-        <v>285.4249758</v>
+        <v>288.631998</v>
       </c>
       <c r="N91">
-        <v>378.8519130888888</v>
+        <v>375.6448908888888</v>
       </c>
       <c r="O91">
-        <v>113.6555739266666</v>
+        <v>112.6934672666666</v>
       </c>
       <c r="P91">
-        <v>265.1963391622222</v>
+        <v>262.9514236222222</v>
       </c>
       <c r="Q91">
-        <v>265.8083391622222</v>
+        <v>263.5634236222222</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4212449855558618</v>
+        <v>0.4570992133715648</v>
       </c>
       <c r="T91">
-        <v>5.463182005639305</v>
+        <v>5.984904707405677</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.327325725532702</v>
+        <v>2.301466550804561</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09346392133715647</v>
+        <v>0.09336749426316816</v>
       </c>
       <c r="C92">
-        <v>573.8391252467704</v>
+        <v>533.8436140959411</v>
       </c>
       <c r="D92">
-        <v>2888.34912524677</v>
+        <v>2890.662614095941</v>
       </c>
       <c r="E92">
-        <v>3154.81</v>
+        <v>3197.119</v>
       </c>
       <c r="F92">
-        <v>3807.81</v>
+        <v>3850.119</v>
       </c>
       <c r="G92">
         <v>1493.3</v>
@@ -8837,28 +8837,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M92">
-        <v>288.631998</v>
+        <v>291.8390202</v>
       </c>
       <c r="N92">
-        <v>375.6448908888888</v>
+        <v>372.4378686888888</v>
       </c>
       <c r="O92">
-        <v>112.6934672666666</v>
+        <v>111.7313606066667</v>
       </c>
       <c r="P92">
-        <v>262.9514236222222</v>
+        <v>260.7065080822222</v>
       </c>
       <c r="Q92">
-        <v>263.5634236222222</v>
+        <v>261.3185080822222</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4570992133715648</v>
+        <v>0.5009210473685353</v>
       </c>
       <c r="T92">
-        <v>5.984904707405677</v>
+        <v>6.622565787342356</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.301466550804561</v>
+        <v>2.276175709586928</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09336749426316816</v>
+        <v>0.09327106718917985</v>
       </c>
       <c r="C93">
-        <v>533.8436140959411</v>
+        <v>493.8518119988648</v>
       </c>
       <c r="D93">
-        <v>2890.662614095941</v>
+        <v>2892.979811998865</v>
       </c>
       <c r="E93">
-        <v>3197.119</v>
+        <v>3239.428</v>
       </c>
       <c r="F93">
-        <v>3850.119</v>
+        <v>3892.428</v>
       </c>
       <c r="G93">
         <v>1493.3</v>
@@ -8919,28 +8919,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M93">
-        <v>291.8390202</v>
+        <v>295.0460424</v>
       </c>
       <c r="N93">
-        <v>372.4378686888888</v>
+        <v>369.2308464888888</v>
       </c>
       <c r="O93">
-        <v>111.7313606066667</v>
+        <v>110.7692539466666</v>
       </c>
       <c r="P93">
-        <v>260.7065080822222</v>
+        <v>258.4615925422221</v>
       </c>
       <c r="Q93">
-        <v>261.3185080822222</v>
+        <v>259.0735925422222</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5009210473685353</v>
+        <v>0.5556983398647484</v>
       </c>
       <c r="T93">
-        <v>6.622565787342356</v>
+        <v>7.419642137263206</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.276175709586928</v>
+        <v>2.251434669265331</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09327106718917985</v>
+        <v>0.09317464011519153</v>
       </c>
       <c r="C94">
-        <v>493.8518119988648</v>
+        <v>453.8637278823962</v>
       </c>
       <c r="D94">
-        <v>2892.979811998865</v>
+        <v>2895.300727882396</v>
       </c>
       <c r="E94">
-        <v>3239.428</v>
+        <v>3281.737</v>
       </c>
       <c r="F94">
-        <v>3892.428</v>
+        <v>3934.737</v>
       </c>
       <c r="G94">
         <v>1493.3</v>
@@ -9001,28 +9001,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M94">
-        <v>295.0460424</v>
+        <v>298.2530646</v>
       </c>
       <c r="N94">
-        <v>369.2308464888888</v>
+        <v>366.0238242888888</v>
       </c>
       <c r="O94">
-        <v>110.7692539466666</v>
+        <v>109.8071472866666</v>
       </c>
       <c r="P94">
-        <v>258.4615925422221</v>
+        <v>256.2166770022222</v>
       </c>
       <c r="Q94">
-        <v>259.0735925422222</v>
+        <v>256.8286770022222</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5556983398647484</v>
+        <v>0.6261262873598794</v>
       </c>
       <c r="T94">
-        <v>7.419642137263206</v>
+        <v>8.44445458716144</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.251434669265331</v>
+        <v>2.227225694326994</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09317464011519153</v>
+        <v>0.09307821304120323</v>
       </c>
       <c r="C95">
-        <v>453.8637278823962</v>
+        <v>413.8793707020563</v>
       </c>
       <c r="D95">
-        <v>2895.300727882396</v>
+        <v>2897.625370702056</v>
       </c>
       <c r="E95">
-        <v>3281.737</v>
+        <v>3324.046</v>
       </c>
       <c r="F95">
-        <v>3934.737</v>
+        <v>3977.046</v>
       </c>
       <c r="G95">
         <v>1493.3</v>
@@ -9083,28 +9083,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M95">
-        <v>298.2530646</v>
+        <v>301.4600868</v>
       </c>
       <c r="N95">
-        <v>366.0238242888888</v>
+        <v>362.8168020888888</v>
       </c>
       <c r="O95">
-        <v>109.8071472866666</v>
+        <v>108.8450406266666</v>
       </c>
       <c r="P95">
-        <v>256.2166770022222</v>
+        <v>253.9717614622222</v>
       </c>
       <c r="Q95">
-        <v>256.8286770022222</v>
+        <v>254.5837614622222</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6261262873598794</v>
+        <v>0.7200302173533877</v>
       </c>
       <c r="T95">
-        <v>8.44445458716144</v>
+        <v>9.810871187025754</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.227225694326994</v>
+        <v>2.203531803961813</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09307821304120323</v>
+        <v>0.0929817859672149</v>
       </c>
       <c r="C96">
-        <v>413.8793707020563</v>
+        <v>373.8987494421531</v>
       </c>
       <c r="D96">
-        <v>2897.625370702056</v>
+        <v>2899.953749442153</v>
       </c>
       <c r="E96">
-        <v>3324.046</v>
+        <v>3366.355</v>
       </c>
       <c r="F96">
-        <v>3977.046</v>
+        <v>4019.355</v>
       </c>
       <c r="G96">
         <v>1493.3</v>
@@ -9165,28 +9165,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M96">
-        <v>301.4600868</v>
+        <v>304.667109</v>
       </c>
       <c r="N96">
-        <v>362.8168020888888</v>
+        <v>359.6097798888888</v>
       </c>
       <c r="O96">
-        <v>108.8450406266666</v>
+        <v>107.8829339666666</v>
       </c>
       <c r="P96">
-        <v>253.9717614622222</v>
+        <v>251.7268459222221</v>
       </c>
       <c r="Q96">
-        <v>254.5837614622222</v>
+        <v>252.3388459222221</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7200302173533877</v>
+        <v>0.8514957193442991</v>
       </c>
       <c r="T96">
-        <v>9.810871187025754</v>
+        <v>11.72385442683579</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.203531803961813</v>
+        <v>2.180336732341162</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0929817859672149</v>
+        <v>0.0928853588932266</v>
       </c>
       <c r="C97">
-        <v>373.8987494421531</v>
+        <v>333.9218731158935</v>
       </c>
       <c r="D97">
-        <v>2899.953749442153</v>
+        <v>2902.285873115893</v>
       </c>
       <c r="E97">
-        <v>3366.355</v>
+        <v>3408.664</v>
       </c>
       <c r="F97">
-        <v>4019.355</v>
+        <v>4061.664</v>
       </c>
       <c r="G97">
         <v>1493.3</v>
@@ -9247,28 +9247,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M97">
-        <v>304.667109</v>
+        <v>307.8741312</v>
       </c>
       <c r="N97">
-        <v>359.6097798888888</v>
+        <v>356.4027576888888</v>
       </c>
       <c r="O97">
-        <v>107.8829339666666</v>
+        <v>106.9208273066666</v>
       </c>
       <c r="P97">
-        <v>251.7268459222221</v>
+        <v>249.4819303822222</v>
       </c>
       <c r="Q97">
-        <v>252.3388459222221</v>
+        <v>250.0939303822222</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8514957193442991</v>
+        <v>1.048693972330667</v>
       </c>
       <c r="T97">
-        <v>11.72385442683579</v>
+        <v>14.59332928655085</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.180336732341162</v>
+        <v>2.157624891379275</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0928853588932266</v>
+        <v>0.09278893181923828</v>
       </c>
       <c r="C98">
-        <v>333.921873115894</v>
+        <v>293.9487507655022</v>
       </c>
       <c r="D98">
-        <v>2902.285873115893</v>
+        <v>2904.621750765502</v>
       </c>
       <c r="E98">
-        <v>3408.663999999999</v>
+        <v>3450.973</v>
       </c>
       <c r="F98">
-        <v>4061.663999999999</v>
+        <v>4103.973</v>
       </c>
       <c r="G98">
         <v>1493.3</v>
@@ -9329,28 +9329,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M98">
-        <v>307.8741312</v>
+        <v>311.0811534</v>
       </c>
       <c r="N98">
-        <v>356.4027576888889</v>
+        <v>353.1957354888888</v>
       </c>
       <c r="O98">
-        <v>106.9208273066667</v>
+        <v>105.9587206466666</v>
       </c>
       <c r="P98">
-        <v>249.4819303822222</v>
+        <v>247.2370148422222</v>
       </c>
       <c r="Q98">
-        <v>250.0939303822222</v>
+        <v>247.8490148422222</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.048693972330664</v>
+        <v>1.377357727307942</v>
       </c>
       <c r="T98">
-        <v>14.59332928655082</v>
+        <v>19.3757873860759</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.157624891379275</v>
+        <v>2.135381335798046</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09278893181923828</v>
+        <v>0.09269250474524997</v>
       </c>
       <c r="C99">
-        <v>293.9487507655022</v>
+        <v>253.9793914623388</v>
       </c>
       <c r="D99">
-        <v>2904.621750765502</v>
+        <v>2906.961391462338</v>
       </c>
       <c r="E99">
-        <v>3450.973</v>
+        <v>3493.281999999999</v>
       </c>
       <c r="F99">
-        <v>4103.973</v>
+        <v>4146.281999999999</v>
       </c>
       <c r="G99">
         <v>1493.3</v>
@@ -9411,28 +9411,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M99">
-        <v>311.0811534</v>
+        <v>314.2881756</v>
       </c>
       <c r="N99">
-        <v>353.1957354888888</v>
+        <v>349.9887132888888</v>
       </c>
       <c r="O99">
-        <v>105.9587206466666</v>
+        <v>104.9966139866666</v>
       </c>
       <c r="P99">
-        <v>247.2370148422222</v>
+        <v>244.9920993022222</v>
       </c>
       <c r="Q99">
-        <v>247.8490148422222</v>
+        <v>245.6040993022222</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.377357727307942</v>
+        <v>2.034685237262496</v>
       </c>
       <c r="T99">
-        <v>19.3757873860759</v>
+        <v>28.94070358512606</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.135381335798046</v>
+        <v>2.113591730330719</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09269250474524997</v>
+        <v>0.09259607767126166</v>
       </c>
       <c r="C100">
-        <v>253.9793914623388</v>
+        <v>214.0138043070101</v>
       </c>
       <c r="D100">
-        <v>2906.961391462338</v>
+        <v>2909.30480430701</v>
       </c>
       <c r="E100">
-        <v>3493.281999999999</v>
+        <v>3535.590999999999</v>
       </c>
       <c r="F100">
-        <v>4146.281999999999</v>
+        <v>4188.590999999999</v>
       </c>
       <c r="G100">
         <v>1493.3</v>
@@ -9493,28 +9493,28 @@
         <v>664.2768888888888</v>
       </c>
       <c r="M100">
-        <v>314.2881756</v>
+        <v>317.4951978</v>
       </c>
       <c r="N100">
-        <v>349.9887132888888</v>
+        <v>346.7816910888889</v>
       </c>
       <c r="O100">
-        <v>104.9966139866666</v>
+        <v>104.0345073266667</v>
       </c>
       <c r="P100">
-        <v>244.9920993022222</v>
+        <v>242.7471837622222</v>
       </c>
       <c r="Q100">
-        <v>245.6040993022222</v>
+        <v>243.3591837622222</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.034685237262496</v>
+        <v>4.006667767126162</v>
       </c>
       <c r="T100">
-        <v>28.94070358512606</v>
+        <v>57.63545218227654</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.113591730330719</v>
+        <v>2.092242318913237</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09259607767126166</v>
-      </c>
-      <c r="C101">
-        <v>214.0138043070101</v>
-      </c>
-      <c r="D101">
-        <v>2909.30480430701</v>
-      </c>
-      <c r="E101">
-        <v>3535.590999999999</v>
-      </c>
-      <c r="F101">
-        <v>4188.590999999999</v>
-      </c>
-      <c r="G101">
-        <v>1493.3</v>
-      </c>
-      <c r="H101">
-        <v>3577.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>664.8888888888888</v>
-      </c>
-      <c r="K101">
-        <v>0.612</v>
-      </c>
-      <c r="L101">
-        <v>664.2768888888888</v>
-      </c>
-      <c r="M101">
-        <v>317.4951978</v>
-      </c>
-      <c r="N101">
-        <v>346.7816910888889</v>
-      </c>
-      <c r="O101">
-        <v>104.0345073266667</v>
-      </c>
-      <c r="P101">
-        <v>242.7471837622222</v>
-      </c>
-      <c r="Q101">
-        <v>243.3591837622222</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.006667767126162</v>
-      </c>
-      <c r="T101">
-        <v>57.63545218227654</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.092242318913237</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
